--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B2" t="n">
-        <v>200.75</v>
+        <v>216.34</v>
       </c>
       <c r="C2" t="n">
-        <v>194.28</v>
+        <v>209.23</v>
       </c>
       <c r="D2" t="n">
-        <v>192.36</v>
+        <v>203.11</v>
       </c>
       <c r="E2" t="n">
-        <v>180.95</v>
+        <v>200.36</v>
       </c>
       <c r="F2" t="n">
-        <v>170.83</v>
+        <v>202.66</v>
       </c>
       <c r="G2" t="n">
-        <v>180.95</v>
+        <v>207.69</v>
       </c>
       <c r="H2" t="n">
-        <v>187.02</v>
+        <v>229.87</v>
       </c>
       <c r="I2" t="n">
-        <v>190.23</v>
+        <v>255.03</v>
       </c>
       <c r="J2" t="n">
-        <v>164.61</v>
+        <v>264.64</v>
       </c>
       <c r="K2" t="n">
-        <v>77.58</v>
+        <v>212.59</v>
       </c>
       <c r="L2" t="n">
-        <v>0.32</v>
+        <v>127.21</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.14</v>
+        <v>59.82</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.28</v>
+        <v>44.53</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>47.51</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.01</v>
+        <v>49.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.01</v>
+        <v>62</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>80.56</v>
       </c>
       <c r="S2" t="n">
-        <v>0.48</v>
+        <v>114.2</v>
       </c>
       <c r="T2" t="n">
-        <v>77.78</v>
+        <v>181.34</v>
       </c>
       <c r="U2" t="n">
-        <v>191.49</v>
+        <v>246.08</v>
       </c>
       <c r="V2" t="n">
-        <v>233.83</v>
+        <v>296.25</v>
       </c>
       <c r="W2" t="n">
-        <v>232.37</v>
+        <v>279.12</v>
       </c>
       <c r="X2" t="n">
-        <v>227.46</v>
+        <v>245.96</v>
       </c>
       <c r="Y2" t="n">
-        <v>210.59</v>
+        <v>224.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>121.39</v>
+        <v>177.48</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>226.06</v>
+        <v>261.43</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>233.1</v>
+        <v>287.68</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22h-24h</t>
+          <t>6h-8h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>219.02</v>
+        <v>242.45</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9h-18h</t>
+          <t>10h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,110 +647,110 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B2" t="n">
-        <v>216.34</v>
+        <v>225.75</v>
       </c>
       <c r="C2" t="n">
-        <v>209.23</v>
+        <v>219.97</v>
       </c>
       <c r="D2" t="n">
-        <v>203.11</v>
+        <v>214.52</v>
       </c>
       <c r="E2" t="n">
-        <v>200.36</v>
+        <v>214.14</v>
       </c>
       <c r="F2" t="n">
-        <v>202.66</v>
+        <v>213.18</v>
       </c>
       <c r="G2" t="n">
-        <v>207.69</v>
+        <v>213.66</v>
       </c>
       <c r="H2" t="n">
-        <v>229.87</v>
+        <v>233.64</v>
       </c>
       <c r="I2" t="n">
-        <v>255.03</v>
+        <v>240.46</v>
       </c>
       <c r="J2" t="n">
-        <v>264.64</v>
+        <v>233.11</v>
       </c>
       <c r="K2" t="n">
-        <v>212.59</v>
+        <v>197.2</v>
       </c>
       <c r="L2" t="n">
-        <v>127.21</v>
+        <v>135.21</v>
       </c>
       <c r="M2" t="n">
-        <v>59.82</v>
+        <v>86.55</v>
       </c>
       <c r="N2" t="n">
-        <v>44.53</v>
+        <v>56</v>
       </c>
       <c r="O2" t="n">
-        <v>47.51</v>
+        <v>38.39</v>
       </c>
       <c r="P2" t="n">
-        <v>49.15</v>
+        <v>49.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>62</v>
+        <v>55.27</v>
       </c>
       <c r="R2" t="n">
-        <v>80.56</v>
+        <v>70.05</v>
       </c>
       <c r="S2" t="n">
-        <v>114.2</v>
+        <v>99.98</v>
       </c>
       <c r="T2" t="n">
-        <v>181.34</v>
+        <v>151.1</v>
       </c>
       <c r="U2" t="n">
-        <v>246.08</v>
+        <v>215.32</v>
       </c>
       <c r="V2" t="n">
-        <v>296.25</v>
+        <v>246.72</v>
       </c>
       <c r="W2" t="n">
-        <v>279.12</v>
+        <v>222.32</v>
       </c>
       <c r="X2" t="n">
-        <v>245.96</v>
+        <v>201.19</v>
       </c>
       <c r="Y2" t="n">
-        <v>224.38</v>
+        <v>183.58</v>
       </c>
       <c r="Z2" t="n">
-        <v>177.48</v>
+        <v>167.38</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>20h-24h</t>
+          <t>4h-8h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>261.43</v>
+        <v>225.24</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>6h-8h</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>237.05</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>20h-22h</t>
         </is>
       </c>
-      <c r="AD2" t="n">
-        <v>287.68</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>6h-8h</t>
-        </is>
-      </c>
       <c r="AF2" t="n">
-        <v>242.45</v>
+        <v>234.52</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-17h</t>
+          <t>10h-18h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B2" t="n">
-        <v>225.75</v>
+        <v>176.77</v>
       </c>
       <c r="C2" t="n">
-        <v>219.97</v>
+        <v>171.29</v>
       </c>
       <c r="D2" t="n">
-        <v>214.52</v>
+        <v>168.78</v>
       </c>
       <c r="E2" t="n">
-        <v>214.14</v>
+        <v>165.12</v>
       </c>
       <c r="F2" t="n">
-        <v>213.18</v>
+        <v>162.55</v>
       </c>
       <c r="G2" t="n">
-        <v>213.66</v>
+        <v>169.78</v>
       </c>
       <c r="H2" t="n">
-        <v>233.64</v>
+        <v>177.35</v>
       </c>
       <c r="I2" t="n">
-        <v>240.46</v>
+        <v>193.98</v>
       </c>
       <c r="J2" t="n">
-        <v>233.11</v>
+        <v>172.86</v>
       </c>
       <c r="K2" t="n">
-        <v>197.2</v>
+        <v>86.72</v>
       </c>
       <c r="L2" t="n">
-        <v>135.21</v>
+        <v>7.86</v>
       </c>
       <c r="M2" t="n">
-        <v>86.55</v>
+        <v>0.53</v>
       </c>
       <c r="N2" t="n">
-        <v>56</v>
+        <v>0.01</v>
       </c>
       <c r="O2" t="n">
-        <v>38.39</v>
+        <v>0.01</v>
       </c>
       <c r="P2" t="n">
-        <v>49.77</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>55.27</v>
+        <v>0.01</v>
       </c>
       <c r="R2" t="n">
-        <v>70.05</v>
+        <v>0.45</v>
       </c>
       <c r="S2" t="n">
-        <v>99.98</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>151.1</v>
+        <v>35.88</v>
       </c>
       <c r="U2" t="n">
-        <v>215.32</v>
+        <v>129.83</v>
       </c>
       <c r="V2" t="n">
-        <v>246.72</v>
+        <v>191.64</v>
       </c>
       <c r="W2" t="n">
-        <v>222.32</v>
+        <v>193.8</v>
       </c>
       <c r="X2" t="n">
-        <v>201.19</v>
+        <v>161.43</v>
       </c>
       <c r="Y2" t="n">
-        <v>183.58</v>
+        <v>141.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>167.38</v>
+        <v>104.64</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,27 +730,27 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>225.24</v>
+        <v>175.92</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>20h-22h</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>192.72</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>6h-8h</t>
         </is>
       </c>
-      <c r="AD2" t="n">
-        <v>237.05</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>20h-22h</t>
-        </is>
-      </c>
       <c r="AF2" t="n">
-        <v>234.52</v>
+        <v>185.66</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-18h</t>
+          <t>9h-18h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,90 +647,90 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B2" t="n">
-        <v>176.77</v>
+        <v>173.7</v>
       </c>
       <c r="C2" t="n">
-        <v>171.29</v>
+        <v>155.99</v>
       </c>
       <c r="D2" t="n">
-        <v>168.78</v>
+        <v>136.13</v>
       </c>
       <c r="E2" t="n">
-        <v>165.12</v>
+        <v>125.46</v>
       </c>
       <c r="F2" t="n">
-        <v>162.55</v>
+        <v>130.46</v>
       </c>
       <c r="G2" t="n">
-        <v>169.78</v>
+        <v>140.52</v>
       </c>
       <c r="H2" t="n">
-        <v>177.35</v>
+        <v>183.54</v>
       </c>
       <c r="I2" t="n">
-        <v>193.98</v>
+        <v>202.43</v>
       </c>
       <c r="J2" t="n">
-        <v>172.86</v>
+        <v>197.72</v>
       </c>
       <c r="K2" t="n">
-        <v>86.72</v>
+        <v>165.02</v>
       </c>
       <c r="L2" t="n">
-        <v>7.86</v>
+        <v>87.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0.53</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01</v>
+        <v>3.27</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01</v>
+        <v>8.18</v>
       </c>
       <c r="R2" t="n">
-        <v>0.45</v>
+        <v>29.86</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>35.88</v>
+        <v>171.36</v>
       </c>
       <c r="U2" t="n">
-        <v>129.83</v>
+        <v>211.19</v>
       </c>
       <c r="V2" t="n">
-        <v>191.64</v>
+        <v>222.04</v>
       </c>
       <c r="W2" t="n">
-        <v>193.8</v>
+        <v>218.62</v>
       </c>
       <c r="X2" t="n">
-        <v>161.43</v>
+        <v>200.71</v>
       </c>
       <c r="Y2" t="n">
-        <v>141.17</v>
+        <v>190.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>104.64</v>
+        <v>127.68</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4h-8h</t>
+          <t>20h-24h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>175.92</v>
+        <v>207.89</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>192.72</v>
+        <v>220.33</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6h-8h</t>
+          <t>22h-24h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>185.66</v>
+        <v>195.44</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9h-18h</t>
+          <t>3h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,110 +647,110 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B2" t="n">
-        <v>173.7</v>
+        <v>187.19</v>
       </c>
       <c r="C2" t="n">
-        <v>155.99</v>
+        <v>180.55</v>
       </c>
       <c r="D2" t="n">
-        <v>136.13</v>
+        <v>179</v>
       </c>
       <c r="E2" t="n">
-        <v>125.46</v>
+        <v>176.19</v>
       </c>
       <c r="F2" t="n">
-        <v>130.46</v>
+        <v>171.59</v>
       </c>
       <c r="G2" t="n">
-        <v>140.52</v>
+        <v>176.95</v>
       </c>
       <c r="H2" t="n">
-        <v>183.54</v>
+        <v>189.63</v>
       </c>
       <c r="I2" t="n">
-        <v>202.43</v>
+        <v>208.5</v>
       </c>
       <c r="J2" t="n">
-        <v>197.72</v>
+        <v>209.43</v>
       </c>
       <c r="K2" t="n">
-        <v>165.02</v>
+        <v>164.11</v>
       </c>
       <c r="L2" t="n">
-        <v>87.37</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>8.470000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="O2" t="n">
-        <v>3.27</v>
+        <v>4.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>5.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.18</v>
+        <v>9.51</v>
       </c>
       <c r="R2" t="n">
-        <v>29.86</v>
+        <v>11.88</v>
       </c>
       <c r="S2" t="n">
-        <v>97.54000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="T2" t="n">
-        <v>171.36</v>
+        <v>127.16</v>
       </c>
       <c r="U2" t="n">
-        <v>211.19</v>
+        <v>191.01</v>
       </c>
       <c r="V2" t="n">
-        <v>222.04</v>
+        <v>202.96</v>
       </c>
       <c r="W2" t="n">
-        <v>218.62</v>
+        <v>186.82</v>
       </c>
       <c r="X2" t="n">
-        <v>200.71</v>
+        <v>171.22</v>
       </c>
       <c r="Y2" t="n">
-        <v>190.18</v>
+        <v>159.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>127.68</v>
+        <v>126.25</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>20h-24h</t>
+          <t>4h-8h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>207.89</v>
+        <v>186.67</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>6h-8h</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>199.06</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>20h-22h</t>
         </is>
       </c>
-      <c r="AD2" t="n">
-        <v>220.33</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>22h-24h</t>
-        </is>
-      </c>
       <c r="AF2" t="n">
-        <v>195.44</v>
+        <v>194.89</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3h-17h</t>
+          <t>10h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,110 +647,110 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B2" t="n">
-        <v>187.19</v>
+        <v>178.84</v>
       </c>
       <c r="C2" t="n">
-        <v>180.55</v>
+        <v>175.34</v>
       </c>
       <c r="D2" t="n">
-        <v>179</v>
+        <v>171.7</v>
       </c>
       <c r="E2" t="n">
-        <v>176.19</v>
+        <v>170</v>
       </c>
       <c r="F2" t="n">
-        <v>171.59</v>
+        <v>172.81</v>
       </c>
       <c r="G2" t="n">
-        <v>176.95</v>
+        <v>174.88</v>
       </c>
       <c r="H2" t="n">
-        <v>189.63</v>
+        <v>181.22</v>
       </c>
       <c r="I2" t="n">
-        <v>208.5</v>
+        <v>187.89</v>
       </c>
       <c r="J2" t="n">
-        <v>209.43</v>
+        <v>169</v>
       </c>
       <c r="K2" t="n">
-        <v>164.11</v>
+        <v>65.81</v>
       </c>
       <c r="L2" t="n">
-        <v>66.68000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5</v>
+        <v>-0.01</v>
       </c>
       <c r="N2" t="n">
-        <v>5.2</v>
+        <v>-0.06</v>
       </c>
       <c r="O2" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.51</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>11.88</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>41.2</v>
+        <v>0.76</v>
       </c>
       <c r="T2" t="n">
-        <v>127.16</v>
+        <v>72.16</v>
       </c>
       <c r="U2" t="n">
-        <v>191.01</v>
+        <v>155.38</v>
       </c>
       <c r="V2" t="n">
-        <v>202.96</v>
+        <v>197.34</v>
       </c>
       <c r="W2" t="n">
-        <v>186.82</v>
+        <v>198.78</v>
       </c>
       <c r="X2" t="n">
-        <v>171.22</v>
+        <v>189.57</v>
       </c>
       <c r="Y2" t="n">
-        <v>159.1</v>
+        <v>186.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>126.25</v>
+        <v>110.35</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4h-8h</t>
+          <t>20h-24h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>186.67</v>
+        <v>193.11</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>6h-8h</t>
+          <t>20h-22h</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>199.06</v>
+        <v>198.06</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>20h-22h</t>
+          <t>22h-24h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>194.89</v>
+        <v>188.16</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-17h</t>
+          <t>9h-18h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B2" t="n">
-        <v>178.84</v>
+        <v>186.02</v>
       </c>
       <c r="C2" t="n">
-        <v>175.34</v>
+        <v>184.82</v>
       </c>
       <c r="D2" t="n">
-        <v>171.7</v>
+        <v>184.68</v>
       </c>
       <c r="E2" t="n">
-        <v>170</v>
+        <v>184.11</v>
       </c>
       <c r="F2" t="n">
-        <v>172.81</v>
+        <v>184.09</v>
       </c>
       <c r="G2" t="n">
-        <v>174.88</v>
+        <v>183.6</v>
       </c>
       <c r="H2" t="n">
-        <v>181.22</v>
+        <v>182.58</v>
       </c>
       <c r="I2" t="n">
-        <v>187.89</v>
+        <v>184.11</v>
       </c>
       <c r="J2" t="n">
-        <v>169</v>
+        <v>161.34</v>
       </c>
       <c r="K2" t="n">
-        <v>65.81</v>
+        <v>33.48</v>
       </c>
       <c r="L2" t="n">
-        <v>0.19</v>
+        <v>-0.01</v>
       </c>
       <c r="M2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O2" t="n">
         <v>-0.01</v>
       </c>
-      <c r="N2" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="S2" t="n">
-        <v>0.76</v>
+        <v>0.13</v>
       </c>
       <c r="T2" t="n">
-        <v>72.16</v>
+        <v>61.8</v>
       </c>
       <c r="U2" t="n">
-        <v>155.38</v>
+        <v>190.15</v>
       </c>
       <c r="V2" t="n">
-        <v>197.34</v>
+        <v>201.52</v>
       </c>
       <c r="W2" t="n">
-        <v>198.78</v>
+        <v>202.97</v>
       </c>
       <c r="X2" t="n">
-        <v>189.57</v>
+        <v>195.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>186.75</v>
+        <v>185.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>110.35</v>
+        <v>112.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>193.11</v>
+        <v>196.33</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>198.06</v>
+        <v>202.24</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>188.16</v>
+        <v>190.41</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B2" t="n">
-        <v>186.02</v>
+        <v>190.83</v>
       </c>
       <c r="C2" t="n">
-        <v>184.82</v>
+        <v>183.42</v>
       </c>
       <c r="D2" t="n">
-        <v>184.68</v>
+        <v>177.86</v>
       </c>
       <c r="E2" t="n">
-        <v>184.11</v>
+        <v>174.58</v>
       </c>
       <c r="F2" t="n">
-        <v>184.09</v>
+        <v>174.4</v>
       </c>
       <c r="G2" t="n">
-        <v>183.6</v>
+        <v>177.82</v>
       </c>
       <c r="H2" t="n">
-        <v>182.58</v>
+        <v>190.58</v>
       </c>
       <c r="I2" t="n">
-        <v>184.11</v>
+        <v>223.32</v>
       </c>
       <c r="J2" t="n">
-        <v>161.34</v>
+        <v>232.78</v>
       </c>
       <c r="K2" t="n">
-        <v>33.48</v>
+        <v>169.2</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.01</v>
+        <v>76.36</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02</v>
+        <v>4.66</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.02</v>
+        <v>1.5</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.01</v>
+        <v>1.73</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.01</v>
+        <v>1.79</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.02</v>
+        <v>4.44</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.02</v>
+        <v>17.97</v>
       </c>
       <c r="S2" t="n">
-        <v>0.13</v>
+        <v>64.75</v>
       </c>
       <c r="T2" t="n">
-        <v>61.8</v>
+        <v>136.14</v>
       </c>
       <c r="U2" t="n">
-        <v>190.15</v>
+        <v>235.84</v>
       </c>
       <c r="V2" t="n">
-        <v>201.52</v>
+        <v>250.72</v>
       </c>
       <c r="W2" t="n">
-        <v>202.97</v>
+        <v>238.82</v>
       </c>
       <c r="X2" t="n">
-        <v>195.02</v>
+        <v>211.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>185.8</v>
+        <v>190.03</v>
       </c>
       <c r="Z2" t="n">
-        <v>112.75</v>
+        <v>138.77</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>196.33</v>
+        <v>222.66</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>202.24</v>
+        <v>244.77</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22h-24h</t>
+          <t>6h-8h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>190.41</v>
+        <v>206.95</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9h-18h</t>
+          <t>10h-18h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B2" t="n">
-        <v>190.83</v>
+        <v>198.6</v>
       </c>
       <c r="C2" t="n">
-        <v>183.42</v>
+        <v>192.68</v>
       </c>
       <c r="D2" t="n">
-        <v>177.86</v>
+        <v>192.56</v>
       </c>
       <c r="E2" t="n">
-        <v>174.58</v>
+        <v>189</v>
       </c>
       <c r="F2" t="n">
-        <v>174.4</v>
+        <v>190</v>
       </c>
       <c r="G2" t="n">
-        <v>177.82</v>
+        <v>189.88</v>
       </c>
       <c r="H2" t="n">
-        <v>190.58</v>
+        <v>203.22</v>
       </c>
       <c r="I2" t="n">
-        <v>223.32</v>
+        <v>234.17</v>
       </c>
       <c r="J2" t="n">
-        <v>232.78</v>
+        <v>249.02</v>
       </c>
       <c r="K2" t="n">
-        <v>169.2</v>
+        <v>169.8</v>
       </c>
       <c r="L2" t="n">
-        <v>76.36</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>4.66</v>
+        <v>39.16</v>
       </c>
       <c r="N2" t="n">
-        <v>1.5</v>
+        <v>22.09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.73</v>
+        <v>10.02</v>
       </c>
       <c r="P2" t="n">
-        <v>1.79</v>
+        <v>17.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.44</v>
+        <v>23.79</v>
       </c>
       <c r="R2" t="n">
-        <v>17.97</v>
+        <v>49</v>
       </c>
       <c r="S2" t="n">
-        <v>64.75</v>
+        <v>105.65</v>
       </c>
       <c r="T2" t="n">
-        <v>136.14</v>
+        <v>161.8</v>
       </c>
       <c r="U2" t="n">
-        <v>235.84</v>
+        <v>251.71</v>
       </c>
       <c r="V2" t="n">
-        <v>250.72</v>
+        <v>282.43</v>
       </c>
       <c r="W2" t="n">
-        <v>238.82</v>
+        <v>262.49</v>
       </c>
       <c r="X2" t="n">
-        <v>211.05</v>
+        <v>235.35</v>
       </c>
       <c r="Y2" t="n">
-        <v>190.03</v>
+        <v>212.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>138.77</v>
+        <v>156.98</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>222.66</v>
+        <v>248.19</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>244.77</v>
+        <v>272.46</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6h-8h</t>
+          <t>22h-24h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>206.95</v>
+        <v>223.92</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-18h</t>
+          <t>10h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="n">
-        <v>198.6</v>
+        <v>204.61</v>
       </c>
       <c r="C2" t="n">
-        <v>192.68</v>
+        <v>201.86</v>
       </c>
       <c r="D2" t="n">
-        <v>192.56</v>
+        <v>196.71</v>
       </c>
       <c r="E2" t="n">
-        <v>189</v>
+        <v>199.69</v>
       </c>
       <c r="F2" t="n">
-        <v>190</v>
+        <v>201.51</v>
       </c>
       <c r="G2" t="n">
-        <v>189.88</v>
+        <v>200.49</v>
       </c>
       <c r="H2" t="n">
-        <v>203.22</v>
+        <v>205.78</v>
       </c>
       <c r="I2" t="n">
-        <v>234.17</v>
+        <v>219.57</v>
       </c>
       <c r="J2" t="n">
-        <v>249.02</v>
+        <v>227.9</v>
       </c>
       <c r="K2" t="n">
-        <v>169.8</v>
+        <v>176.69</v>
       </c>
       <c r="L2" t="n">
-        <v>85.18000000000001</v>
+        <v>118.2</v>
       </c>
       <c r="M2" t="n">
-        <v>39.16</v>
+        <v>85</v>
       </c>
       <c r="N2" t="n">
-        <v>22.09</v>
+        <v>35</v>
       </c>
       <c r="O2" t="n">
-        <v>10.02</v>
+        <v>17.29</v>
       </c>
       <c r="P2" t="n">
-        <v>17.35</v>
+        <v>25.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>23.79</v>
+        <v>31.71</v>
       </c>
       <c r="R2" t="n">
-        <v>49</v>
+        <v>58.44</v>
       </c>
       <c r="S2" t="n">
-        <v>105.65</v>
+        <v>101.43</v>
       </c>
       <c r="T2" t="n">
-        <v>161.8</v>
+        <v>154.88</v>
       </c>
       <c r="U2" t="n">
-        <v>251.71</v>
+        <v>237.23</v>
       </c>
       <c r="V2" t="n">
-        <v>282.43</v>
+        <v>263.89</v>
       </c>
       <c r="W2" t="n">
-        <v>262.49</v>
+        <v>248.34</v>
       </c>
       <c r="X2" t="n">
-        <v>235.35</v>
+        <v>224.85</v>
       </c>
       <c r="Y2" t="n">
-        <v>212.48</v>
+        <v>210.72</v>
       </c>
       <c r="Z2" t="n">
-        <v>156.98</v>
+        <v>160.28</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>248.19</v>
+        <v>236.95</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>272.46</v>
+        <v>256.12</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -746,11 +746,11 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>223.92</v>
+        <v>217.78</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-17h</t>
+          <t>10h-18h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B2" t="n">
-        <v>204.61</v>
+        <v>197.04</v>
       </c>
       <c r="C2" t="n">
-        <v>201.86</v>
+        <v>196.43</v>
       </c>
       <c r="D2" t="n">
-        <v>196.71</v>
+        <v>194.78</v>
       </c>
       <c r="E2" t="n">
-        <v>199.69</v>
+        <v>194.11</v>
       </c>
       <c r="F2" t="n">
-        <v>201.51</v>
+        <v>192.44</v>
       </c>
       <c r="G2" t="n">
-        <v>200.49</v>
+        <v>193.53</v>
       </c>
       <c r="H2" t="n">
-        <v>205.78</v>
+        <v>197</v>
       </c>
       <c r="I2" t="n">
-        <v>219.57</v>
+        <v>211.45</v>
       </c>
       <c r="J2" t="n">
-        <v>227.9</v>
+        <v>224.75</v>
       </c>
       <c r="K2" t="n">
-        <v>176.69</v>
+        <v>177.71</v>
       </c>
       <c r="L2" t="n">
-        <v>118.2</v>
+        <v>104.64</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>97.84</v>
       </c>
       <c r="N2" t="n">
-        <v>35</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>17.29</v>
+        <v>24.76</v>
       </c>
       <c r="P2" t="n">
-        <v>25.05</v>
+        <v>35.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.71</v>
+        <v>39.11</v>
       </c>
       <c r="R2" t="n">
-        <v>58.44</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>101.43</v>
+        <v>95.25</v>
       </c>
       <c r="T2" t="n">
-        <v>154.88</v>
+        <v>150.08</v>
       </c>
       <c r="U2" t="n">
-        <v>237.23</v>
+        <v>234.05</v>
       </c>
       <c r="V2" t="n">
-        <v>263.89</v>
+        <v>279.05</v>
       </c>
       <c r="W2" t="n">
-        <v>248.34</v>
+        <v>258.1</v>
       </c>
       <c r="X2" t="n">
-        <v>224.85</v>
+        <v>210.34</v>
       </c>
       <c r="Y2" t="n">
-        <v>210.72</v>
+        <v>200.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>160.28</v>
+        <v>160.58</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>236.95</v>
+        <v>236.98</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>256.12</v>
+        <v>268.58</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>217.78</v>
+        <v>205.38</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B2" t="n">
-        <v>197.04</v>
+        <v>196.17</v>
       </c>
       <c r="C2" t="n">
-        <v>196.43</v>
+        <v>195.26</v>
       </c>
       <c r="D2" t="n">
-        <v>194.78</v>
+        <v>187.98</v>
       </c>
       <c r="E2" t="n">
-        <v>194.11</v>
+        <v>187.27</v>
       </c>
       <c r="F2" t="n">
-        <v>192.44</v>
+        <v>186.62</v>
       </c>
       <c r="G2" t="n">
-        <v>193.53</v>
+        <v>187.4</v>
       </c>
       <c r="H2" t="n">
-        <v>197</v>
+        <v>200.95</v>
       </c>
       <c r="I2" t="n">
-        <v>211.45</v>
+        <v>236.75</v>
       </c>
       <c r="J2" t="n">
-        <v>224.75</v>
+        <v>237.07</v>
       </c>
       <c r="K2" t="n">
-        <v>177.71</v>
+        <v>186.81</v>
       </c>
       <c r="L2" t="n">
+        <v>124.08</v>
+      </c>
+      <c r="M2" t="n">
+        <v>105.02</v>
+      </c>
+      <c r="N2" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="O2" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="P2" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>40.22</v>
+      </c>
+      <c r="R2" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="S2" t="n">
         <v>104.64</v>
       </c>
-      <c r="M2" t="n">
-        <v>97.84</v>
-      </c>
-      <c r="N2" t="n">
-        <v>72.65000000000001</v>
-      </c>
-      <c r="O2" t="n">
-        <v>24.76</v>
-      </c>
-      <c r="P2" t="n">
-        <v>35.55</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>39.11</v>
-      </c>
-      <c r="R2" t="n">
-        <v>72.76000000000001</v>
-      </c>
-      <c r="S2" t="n">
-        <v>95.25</v>
-      </c>
       <c r="T2" t="n">
-        <v>150.08</v>
+        <v>158.75</v>
       </c>
       <c r="U2" t="n">
-        <v>234.05</v>
+        <v>239.56</v>
       </c>
       <c r="V2" t="n">
-        <v>279.05</v>
+        <v>255.28</v>
       </c>
       <c r="W2" t="n">
-        <v>258.1</v>
+        <v>227.32</v>
       </c>
       <c r="X2" t="n">
-        <v>210.34</v>
+        <v>207.81</v>
       </c>
       <c r="Y2" t="n">
-        <v>200.42</v>
+        <v>194.96</v>
       </c>
       <c r="Z2" t="n">
-        <v>160.58</v>
+        <v>161.38</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>236.98</v>
+        <v>221.34</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,15 +738,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>268.58</v>
+        <v>241.3</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22h-24h</t>
+          <t>6h-8h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>205.38</v>
+        <v>218.85</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B2" t="n">
-        <v>196.17</v>
+        <v>197.99</v>
       </c>
       <c r="C2" t="n">
-        <v>195.26</v>
+        <v>185.74</v>
       </c>
       <c r="D2" t="n">
-        <v>187.98</v>
+        <v>183.83</v>
       </c>
       <c r="E2" t="n">
-        <v>187.27</v>
+        <v>183.4</v>
       </c>
       <c r="F2" t="n">
-        <v>186.62</v>
+        <v>184.06</v>
       </c>
       <c r="G2" t="n">
-        <v>187.4</v>
+        <v>184.14</v>
       </c>
       <c r="H2" t="n">
-        <v>200.95</v>
+        <v>185.7</v>
       </c>
       <c r="I2" t="n">
-        <v>236.75</v>
+        <v>196.04</v>
       </c>
       <c r="J2" t="n">
-        <v>237.07</v>
+        <v>193.16</v>
       </c>
       <c r="K2" t="n">
-        <v>186.81</v>
+        <v>152.35</v>
       </c>
       <c r="L2" t="n">
-        <v>124.08</v>
+        <v>59.53</v>
       </c>
       <c r="M2" t="n">
-        <v>105.02</v>
+        <v>2.71</v>
       </c>
       <c r="N2" t="n">
-        <v>74.25</v>
+        <v>1.75</v>
       </c>
       <c r="O2" t="n">
-        <v>30.57</v>
+        <v>1.03</v>
       </c>
       <c r="P2" t="n">
-        <v>34.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>40.22</v>
+        <v>0.48</v>
       </c>
       <c r="R2" t="n">
-        <v>74.29000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="S2" t="n">
-        <v>104.64</v>
+        <v>38.46</v>
       </c>
       <c r="T2" t="n">
-        <v>158.75</v>
+        <v>142.15</v>
       </c>
       <c r="U2" t="n">
-        <v>239.56</v>
+        <v>222.18</v>
       </c>
       <c r="V2" t="n">
-        <v>255.28</v>
+        <v>226.36</v>
       </c>
       <c r="W2" t="n">
-        <v>227.32</v>
+        <v>208.49</v>
       </c>
       <c r="X2" t="n">
-        <v>207.81</v>
+        <v>199.31</v>
       </c>
       <c r="Y2" t="n">
-        <v>194.96</v>
+        <v>186</v>
       </c>
       <c r="Z2" t="n">
-        <v>161.38</v>
+        <v>130.68</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>221.34</v>
+        <v>205.04</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>241.3</v>
+        <v>217.42</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6h-8h</t>
+          <t>22h-24h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>218.85</v>
+        <v>192.66</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-18h</t>
+          <t>10h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B2" t="n">
-        <v>197.99</v>
+        <v>183.81</v>
       </c>
       <c r="C2" t="n">
-        <v>185.74</v>
+        <v>178.33</v>
       </c>
       <c r="D2" t="n">
-        <v>183.83</v>
+        <v>171.34</v>
       </c>
       <c r="E2" t="n">
-        <v>183.4</v>
+        <v>166.43</v>
       </c>
       <c r="F2" t="n">
-        <v>184.06</v>
+        <v>161.57</v>
       </c>
       <c r="G2" t="n">
-        <v>184.14</v>
+        <v>158.67</v>
       </c>
       <c r="H2" t="n">
-        <v>185.7</v>
+        <v>160</v>
       </c>
       <c r="I2" t="n">
-        <v>196.04</v>
+        <v>168.18</v>
       </c>
       <c r="J2" t="n">
-        <v>193.16</v>
+        <v>155.12</v>
       </c>
       <c r="K2" t="n">
-        <v>152.35</v>
+        <v>83.31</v>
       </c>
       <c r="L2" t="n">
-        <v>59.53</v>
+        <v>15.29</v>
       </c>
       <c r="M2" t="n">
-        <v>2.71</v>
+        <v>0.22</v>
       </c>
       <c r="N2" t="n">
-        <v>1.75</v>
+        <v>0.16</v>
       </c>
       <c r="O2" t="n">
-        <v>1.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.48</v>
+        <v>-0.01</v>
       </c>
       <c r="R2" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>38.46</v>
+        <v>56.93</v>
       </c>
       <c r="T2" t="n">
-        <v>142.15</v>
+        <v>151.44</v>
       </c>
       <c r="U2" t="n">
-        <v>222.18</v>
+        <v>193.74</v>
       </c>
       <c r="V2" t="n">
-        <v>226.36</v>
+        <v>196.64</v>
       </c>
       <c r="W2" t="n">
-        <v>208.49</v>
+        <v>185.26</v>
       </c>
       <c r="X2" t="n">
-        <v>199.31</v>
+        <v>175.23</v>
       </c>
       <c r="Y2" t="n">
-        <v>186</v>
+        <v>165.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>130.68</v>
+        <v>113.68</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>205.04</v>
+        <v>180.56</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>217.42</v>
+        <v>190.95</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22h-24h</t>
+          <t>0h-2h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>192.66</v>
+        <v>181.07</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-17h</t>
+          <t>9h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,90 +647,90 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B2" t="n">
-        <v>183.81</v>
+        <v>167.87</v>
       </c>
       <c r="C2" t="n">
-        <v>178.33</v>
+        <v>165.98</v>
       </c>
       <c r="D2" t="n">
-        <v>171.34</v>
+        <v>159.11</v>
       </c>
       <c r="E2" t="n">
-        <v>166.43</v>
+        <v>157.88</v>
       </c>
       <c r="F2" t="n">
-        <v>161.57</v>
+        <v>162.7</v>
       </c>
       <c r="G2" t="n">
-        <v>158.67</v>
+        <v>176.59</v>
       </c>
       <c r="H2" t="n">
-        <v>160</v>
+        <v>211.13</v>
       </c>
       <c r="I2" t="n">
-        <v>168.18</v>
+        <v>241.39</v>
       </c>
       <c r="J2" t="n">
-        <v>155.12</v>
+        <v>250</v>
       </c>
       <c r="K2" t="n">
-        <v>83.31</v>
+        <v>236.02</v>
       </c>
       <c r="L2" t="n">
-        <v>15.29</v>
+        <v>221.68</v>
       </c>
       <c r="M2" t="n">
-        <v>0.22</v>
+        <v>189.86</v>
       </c>
       <c r="N2" t="n">
-        <v>0.16</v>
+        <v>158.19</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07000000000000001</v>
+        <v>150.32</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>157.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.01</v>
+        <v>167.47</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>194.16</v>
       </c>
       <c r="S2" t="n">
-        <v>56.93</v>
+        <v>232.45</v>
       </c>
       <c r="T2" t="n">
-        <v>151.44</v>
+        <v>233.31</v>
       </c>
       <c r="U2" t="n">
-        <v>193.74</v>
+        <v>236.7</v>
       </c>
       <c r="V2" t="n">
-        <v>196.64</v>
+        <v>265.67</v>
       </c>
       <c r="W2" t="n">
-        <v>185.26</v>
+        <v>230.21</v>
       </c>
       <c r="X2" t="n">
-        <v>175.23</v>
+        <v>203.35</v>
       </c>
       <c r="Y2" t="n">
-        <v>165.09</v>
+        <v>184.76</v>
       </c>
       <c r="Z2" t="n">
-        <v>113.68</v>
+        <v>198.1</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>20h-24h</t>
+          <t>8h-12h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>180.56</v>
+        <v>224.39</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>190.95</v>
+        <v>247.94</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0h-2h</t>
+          <t>8h-10h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>181.07</v>
+        <v>243.01</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9h-17h</t>
+          <t>0h-23h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,110 +647,110 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B2" t="n">
-        <v>167.87</v>
+        <v>209.8</v>
       </c>
       <c r="C2" t="n">
-        <v>165.98</v>
+        <v>202.51</v>
       </c>
       <c r="D2" t="n">
-        <v>159.11</v>
+        <v>186.07</v>
       </c>
       <c r="E2" t="n">
-        <v>157.88</v>
+        <v>175.04</v>
       </c>
       <c r="F2" t="n">
-        <v>162.7</v>
+        <v>162.52</v>
       </c>
       <c r="G2" t="n">
-        <v>176.59</v>
+        <v>167.69</v>
       </c>
       <c r="H2" t="n">
-        <v>211.13</v>
+        <v>190.7</v>
       </c>
       <c r="I2" t="n">
-        <v>241.39</v>
+        <v>224.15</v>
       </c>
       <c r="J2" t="n">
-        <v>250</v>
+        <v>220.1</v>
       </c>
       <c r="K2" t="n">
-        <v>236.02</v>
+        <v>172.8</v>
       </c>
       <c r="L2" t="n">
-        <v>221.68</v>
+        <v>87.34</v>
       </c>
       <c r="M2" t="n">
-        <v>189.86</v>
+        <v>15.22</v>
       </c>
       <c r="N2" t="n">
-        <v>158.19</v>
+        <v>3.89</v>
       </c>
       <c r="O2" t="n">
-        <v>150.32</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
-        <v>157.6</v>
+        <v>1.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>167.47</v>
+        <v>1.11</v>
       </c>
       <c r="R2" t="n">
-        <v>194.16</v>
+        <v>4.08</v>
       </c>
       <c r="S2" t="n">
-        <v>232.45</v>
+        <v>55.25</v>
       </c>
       <c r="T2" t="n">
-        <v>233.31</v>
+        <v>121.98</v>
       </c>
       <c r="U2" t="n">
-        <v>236.7</v>
+        <v>204.75</v>
       </c>
       <c r="V2" t="n">
-        <v>265.67</v>
+        <v>213.02</v>
       </c>
       <c r="W2" t="n">
-        <v>230.21</v>
+        <v>181.41</v>
       </c>
       <c r="X2" t="n">
-        <v>203.35</v>
+        <v>172.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>184.76</v>
+        <v>147.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>198.1</v>
+        <v>130.1</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>8h-12h</t>
+          <t>0h-4h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>224.39</v>
+        <v>193.36</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>20h-22h</t>
+          <t>6h-8h</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>247.94</v>
+        <v>207.42</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8h-10h</t>
+          <t>0h-2h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>243.01</v>
+        <v>206.16</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0h-23h</t>
+          <t>10h-18h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,110 +647,110 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>209.8</v>
+        <v>133.35</v>
       </c>
       <c r="C2" t="n">
-        <v>202.51</v>
+        <v>132.56</v>
       </c>
       <c r="D2" t="n">
-        <v>186.07</v>
+        <v>133.35</v>
       </c>
       <c r="E2" t="n">
-        <v>175.04</v>
+        <v>138.11</v>
       </c>
       <c r="F2" t="n">
-        <v>162.52</v>
+        <v>136.68</v>
       </c>
       <c r="G2" t="n">
-        <v>167.69</v>
+        <v>153.94</v>
       </c>
       <c r="H2" t="n">
-        <v>190.7</v>
+        <v>169.13</v>
       </c>
       <c r="I2" t="n">
-        <v>224.15</v>
+        <v>204.69</v>
       </c>
       <c r="J2" t="n">
-        <v>220.1</v>
+        <v>205.32</v>
       </c>
       <c r="K2" t="n">
-        <v>172.8</v>
+        <v>180.72</v>
       </c>
       <c r="L2" t="n">
-        <v>87.34</v>
+        <v>159.64</v>
       </c>
       <c r="M2" t="n">
-        <v>15.22</v>
+        <v>125.57</v>
       </c>
       <c r="N2" t="n">
-        <v>3.89</v>
+        <v>105.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.11</v>
+        <v>114.18</v>
       </c>
       <c r="R2" t="n">
-        <v>4.08</v>
+        <v>128.12</v>
       </c>
       <c r="S2" t="n">
-        <v>55.25</v>
+        <v>168.38</v>
       </c>
       <c r="T2" t="n">
-        <v>121.98</v>
+        <v>214.28</v>
       </c>
       <c r="U2" t="n">
-        <v>204.75</v>
+        <v>242.07</v>
       </c>
       <c r="V2" t="n">
-        <v>213.02</v>
+        <v>267.38</v>
       </c>
       <c r="W2" t="n">
-        <v>181.41</v>
+        <v>336.51</v>
       </c>
       <c r="X2" t="n">
-        <v>172.9</v>
+        <v>230.37</v>
       </c>
       <c r="Y2" t="n">
-        <v>147.4</v>
+        <v>217.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>130.1</v>
+        <v>170.1</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0h-4h</t>
+          <t>20h-24h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>193.36</v>
+        <v>262.88</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>6h-8h</t>
+          <t>20h-22h</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>207.42</v>
+        <v>301.94</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0h-2h</t>
+          <t>18h-20h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>206.16</v>
+        <v>228.18</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-18h</t>
+          <t>0h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B2" t="n">
-        <v>133.35</v>
+        <v>190.04</v>
       </c>
       <c r="C2" t="n">
-        <v>132.56</v>
+        <v>194.07</v>
       </c>
       <c r="D2" t="n">
-        <v>133.35</v>
+        <v>183.41</v>
       </c>
       <c r="E2" t="n">
-        <v>138.11</v>
+        <v>184.78</v>
       </c>
       <c r="F2" t="n">
-        <v>136.68</v>
+        <v>179.43</v>
       </c>
       <c r="G2" t="n">
-        <v>153.94</v>
+        <v>174.04</v>
       </c>
       <c r="H2" t="n">
-        <v>169.13</v>
+        <v>194.73</v>
       </c>
       <c r="I2" t="n">
-        <v>204.69</v>
+        <v>214.44</v>
       </c>
       <c r="J2" t="n">
-        <v>205.32</v>
+        <v>211.26</v>
       </c>
       <c r="K2" t="n">
-        <v>180.72</v>
+        <v>189.58</v>
       </c>
       <c r="L2" t="n">
-        <v>159.64</v>
+        <v>126.14</v>
       </c>
       <c r="M2" t="n">
-        <v>125.57</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>105.2</v>
+        <v>48.01</v>
       </c>
       <c r="O2" t="n">
-        <v>89.06999999999999</v>
+        <v>42.6</v>
       </c>
       <c r="P2" t="n">
-        <v>96.59999999999999</v>
+        <v>39.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>114.18</v>
+        <v>44.78</v>
       </c>
       <c r="R2" t="n">
-        <v>128.12</v>
+        <v>60.73</v>
       </c>
       <c r="S2" t="n">
-        <v>168.38</v>
+        <v>87.73</v>
       </c>
       <c r="T2" t="n">
-        <v>214.28</v>
+        <v>148.04</v>
       </c>
       <c r="U2" t="n">
-        <v>242.07</v>
+        <v>212.99</v>
       </c>
       <c r="V2" t="n">
-        <v>267.38</v>
+        <v>242.24</v>
       </c>
       <c r="W2" t="n">
-        <v>336.51</v>
+        <v>221.44</v>
       </c>
       <c r="X2" t="n">
-        <v>230.37</v>
+        <v>202.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>217.27</v>
+        <v>181.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>170.1</v>
+        <v>152.01</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>262.88</v>
+        <v>211.83</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>301.94</v>
+        <v>231.84</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>18h-20h</t>
+          <t>6h-8h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>228.18</v>
+        <v>204.58</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0h-17h</t>
+          <t>10h-18h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B2" t="n">
-        <v>190.04</v>
+        <v>176.41</v>
       </c>
       <c r="C2" t="n">
-        <v>194.07</v>
+        <v>165.47</v>
       </c>
       <c r="D2" t="n">
-        <v>183.41</v>
+        <v>161.71</v>
       </c>
       <c r="E2" t="n">
-        <v>184.78</v>
+        <v>160.66</v>
       </c>
       <c r="F2" t="n">
-        <v>179.43</v>
+        <v>163.67</v>
       </c>
       <c r="G2" t="n">
-        <v>174.04</v>
+        <v>177.87</v>
       </c>
       <c r="H2" t="n">
-        <v>194.73</v>
+        <v>214.97</v>
       </c>
       <c r="I2" t="n">
-        <v>214.44</v>
+        <v>236.66</v>
       </c>
       <c r="J2" t="n">
-        <v>211.26</v>
+        <v>257.07</v>
       </c>
       <c r="K2" t="n">
-        <v>189.58</v>
+        <v>199.67</v>
       </c>
       <c r="L2" t="n">
-        <v>126.14</v>
+        <v>153.85</v>
       </c>
       <c r="M2" t="n">
-        <v>75.06999999999999</v>
+        <v>122.57</v>
       </c>
       <c r="N2" t="n">
-        <v>48.01</v>
+        <v>119.35</v>
       </c>
       <c r="O2" t="n">
-        <v>42.6</v>
+        <v>116.92</v>
       </c>
       <c r="P2" t="n">
-        <v>39.06</v>
+        <v>114.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.78</v>
+        <v>119.32</v>
       </c>
       <c r="R2" t="n">
-        <v>60.73</v>
+        <v>123.76</v>
       </c>
       <c r="S2" t="n">
-        <v>87.73</v>
+        <v>144.91</v>
       </c>
       <c r="T2" t="n">
-        <v>148.04</v>
+        <v>201.18</v>
       </c>
       <c r="U2" t="n">
-        <v>212.99</v>
+        <v>239.72</v>
       </c>
       <c r="V2" t="n">
-        <v>242.24</v>
+        <v>267.39</v>
       </c>
       <c r="W2" t="n">
-        <v>221.44</v>
+        <v>229.96</v>
       </c>
       <c r="X2" t="n">
-        <v>202.36</v>
+        <v>203.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>181.29</v>
+        <v>194.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>152.01</v>
+        <v>177.72</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>211.83</v>
+        <v>223.79</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>231.84</v>
+        <v>248.68</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6h-8h</t>
+          <t>8h-10h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>204.58</v>
+        <v>228.37</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-18h</t>
+          <t>0h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B2" t="n">
-        <v>176.41</v>
+        <v>194.82</v>
       </c>
       <c r="C2" t="n">
-        <v>165.47</v>
+        <v>179.5</v>
       </c>
       <c r="D2" t="n">
-        <v>161.71</v>
+        <v>173.51</v>
       </c>
       <c r="E2" t="n">
-        <v>160.66</v>
+        <v>169.11</v>
       </c>
       <c r="F2" t="n">
-        <v>163.67</v>
+        <v>166.07</v>
       </c>
       <c r="G2" t="n">
-        <v>177.87</v>
+        <v>169.9</v>
       </c>
       <c r="H2" t="n">
-        <v>214.97</v>
+        <v>182.25</v>
       </c>
       <c r="I2" t="n">
-        <v>236.66</v>
+        <v>199.98</v>
       </c>
       <c r="J2" t="n">
-        <v>257.07</v>
+        <v>189.21</v>
       </c>
       <c r="K2" t="n">
-        <v>199.67</v>
+        <v>177.35</v>
       </c>
       <c r="L2" t="n">
-        <v>153.85</v>
+        <v>166.13</v>
       </c>
       <c r="M2" t="n">
-        <v>122.57</v>
+        <v>135.6</v>
       </c>
       <c r="N2" t="n">
-        <v>119.35</v>
+        <v>97.45</v>
       </c>
       <c r="O2" t="n">
-        <v>116.92</v>
+        <v>68.94</v>
       </c>
       <c r="P2" t="n">
-        <v>114.38</v>
+        <v>81.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>119.32</v>
+        <v>111.08</v>
       </c>
       <c r="R2" t="n">
-        <v>123.76</v>
+        <v>130.53</v>
       </c>
       <c r="S2" t="n">
-        <v>144.91</v>
+        <v>153.06</v>
       </c>
       <c r="T2" t="n">
-        <v>201.18</v>
+        <v>188.26</v>
       </c>
       <c r="U2" t="n">
-        <v>239.72</v>
+        <v>222.11</v>
       </c>
       <c r="V2" t="n">
-        <v>267.39</v>
+        <v>223.69</v>
       </c>
       <c r="W2" t="n">
-        <v>229.96</v>
+        <v>215.19</v>
       </c>
       <c r="X2" t="n">
-        <v>203.11</v>
+        <v>208.51</v>
       </c>
       <c r="Y2" t="n">
-        <v>194.7</v>
+        <v>195.01</v>
       </c>
       <c r="Z2" t="n">
-        <v>177.72</v>
+        <v>166.6</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>223.79</v>
+        <v>210.6</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>248.68</v>
+        <v>219.44</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8h-10h</t>
+          <t>18h-20h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>228.37</v>
+        <v>205.18</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0h-17h</t>
+          <t>4h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B2" t="n">
-        <v>194.82</v>
+        <v>204.73</v>
       </c>
       <c r="C2" t="n">
-        <v>179.5</v>
+        <v>195.34</v>
       </c>
       <c r="D2" t="n">
-        <v>173.51</v>
+        <v>191.35</v>
       </c>
       <c r="E2" t="n">
-        <v>169.11</v>
+        <v>187.23</v>
       </c>
       <c r="F2" t="n">
-        <v>166.07</v>
+        <v>189.46</v>
       </c>
       <c r="G2" t="n">
-        <v>169.9</v>
+        <v>178.98</v>
       </c>
       <c r="H2" t="n">
-        <v>182.25</v>
+        <v>181.26</v>
       </c>
       <c r="I2" t="n">
-        <v>199.98</v>
+        <v>188.62</v>
       </c>
       <c r="J2" t="n">
-        <v>189.21</v>
+        <v>195.72</v>
       </c>
       <c r="K2" t="n">
-        <v>177.35</v>
+        <v>185.38</v>
       </c>
       <c r="L2" t="n">
-        <v>166.13</v>
+        <v>156.71</v>
       </c>
       <c r="M2" t="n">
-        <v>135.6</v>
+        <v>118.72</v>
       </c>
       <c r="N2" t="n">
-        <v>97.45</v>
+        <v>90.67</v>
       </c>
       <c r="O2" t="n">
-        <v>68.94</v>
+        <v>80.25</v>
       </c>
       <c r="P2" t="n">
-        <v>81.19</v>
+        <v>77.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>111.08</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>130.53</v>
+        <v>132.75</v>
       </c>
       <c r="S2" t="n">
-        <v>153.06</v>
+        <v>163.66</v>
       </c>
       <c r="T2" t="n">
-        <v>188.26</v>
+        <v>209.63</v>
       </c>
       <c r="U2" t="n">
-        <v>222.11</v>
+        <v>233.97</v>
       </c>
       <c r="V2" t="n">
-        <v>223.69</v>
+        <v>229.92</v>
       </c>
       <c r="W2" t="n">
-        <v>215.19</v>
+        <v>217</v>
       </c>
       <c r="X2" t="n">
-        <v>208.51</v>
+        <v>213.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>195.01</v>
+        <v>210.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>166.6</v>
+        <v>171.85</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>210.6</v>
+        <v>217.74</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>219.44</v>
+        <v>223.46</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -746,11 +746,11 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>205.18</v>
+        <v>221.8</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>4h-17h</t>
+          <t>10h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B2" t="n">
-        <v>204.73</v>
+        <v>207.7</v>
       </c>
       <c r="C2" t="n">
-        <v>195.34</v>
+        <v>203.46</v>
       </c>
       <c r="D2" t="n">
-        <v>191.35</v>
+        <v>195.3</v>
       </c>
       <c r="E2" t="n">
-        <v>187.23</v>
+        <v>192.75</v>
       </c>
       <c r="F2" t="n">
-        <v>189.46</v>
+        <v>192.66</v>
       </c>
       <c r="G2" t="n">
-        <v>178.98</v>
+        <v>195.15</v>
       </c>
       <c r="H2" t="n">
-        <v>181.26</v>
+        <v>208.43</v>
       </c>
       <c r="I2" t="n">
-        <v>188.62</v>
+        <v>229.97</v>
       </c>
       <c r="J2" t="n">
-        <v>195.72</v>
+        <v>240.06</v>
       </c>
       <c r="K2" t="n">
-        <v>185.38</v>
+        <v>215.11</v>
       </c>
       <c r="L2" t="n">
-        <v>156.71</v>
+        <v>191.48</v>
       </c>
       <c r="M2" t="n">
-        <v>118.72</v>
+        <v>149.31</v>
       </c>
       <c r="N2" t="n">
-        <v>90.67</v>
+        <v>135.34</v>
       </c>
       <c r="O2" t="n">
-        <v>80.25</v>
+        <v>135.14</v>
       </c>
       <c r="P2" t="n">
-        <v>77.77</v>
+        <v>130.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>91.20999999999999</v>
+        <v>139.8</v>
       </c>
       <c r="R2" t="n">
-        <v>132.75</v>
+        <v>156.31</v>
       </c>
       <c r="S2" t="n">
-        <v>163.66</v>
+        <v>191.21</v>
       </c>
       <c r="T2" t="n">
-        <v>209.63</v>
+        <v>219.06</v>
       </c>
       <c r="U2" t="n">
-        <v>233.97</v>
+        <v>258.15</v>
       </c>
       <c r="V2" t="n">
-        <v>229.92</v>
+        <v>268.39</v>
       </c>
       <c r="W2" t="n">
-        <v>217</v>
+        <v>262.64</v>
       </c>
       <c r="X2" t="n">
-        <v>213.87</v>
+        <v>220.83</v>
       </c>
       <c r="Y2" t="n">
-        <v>210.16</v>
+        <v>212.41</v>
       </c>
       <c r="Z2" t="n">
-        <v>171.85</v>
+        <v>197.97</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>217.74</v>
+        <v>241.07</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>223.46</v>
+        <v>265.52</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -746,11 +746,11 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>221.8</v>
+        <v>238.6</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-17h</t>
+          <t>2h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B2" t="n">
-        <v>207.7</v>
+        <v>205.91</v>
       </c>
       <c r="C2" t="n">
-        <v>203.46</v>
+        <v>200.04</v>
       </c>
       <c r="D2" t="n">
-        <v>195.3</v>
+        <v>195.41</v>
       </c>
       <c r="E2" t="n">
-        <v>192.75</v>
+        <v>190.77</v>
       </c>
       <c r="F2" t="n">
-        <v>192.66</v>
+        <v>189.6</v>
       </c>
       <c r="G2" t="n">
-        <v>195.15</v>
+        <v>189.79</v>
       </c>
       <c r="H2" t="n">
-        <v>208.43</v>
+        <v>208.36</v>
       </c>
       <c r="I2" t="n">
-        <v>229.97</v>
+        <v>236.58</v>
       </c>
       <c r="J2" t="n">
-        <v>240.06</v>
+        <v>245.09</v>
       </c>
       <c r="K2" t="n">
-        <v>215.11</v>
+        <v>243.11</v>
       </c>
       <c r="L2" t="n">
-        <v>191.48</v>
+        <v>202.13</v>
       </c>
       <c r="M2" t="n">
-        <v>149.31</v>
+        <v>187.4</v>
       </c>
       <c r="N2" t="n">
-        <v>135.34</v>
+        <v>170.02</v>
       </c>
       <c r="O2" t="n">
-        <v>135.14</v>
+        <v>163.33</v>
       </c>
       <c r="P2" t="n">
-        <v>130.55</v>
+        <v>151.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>139.8</v>
+        <v>164.5</v>
       </c>
       <c r="R2" t="n">
-        <v>156.31</v>
+        <v>170.21</v>
       </c>
       <c r="S2" t="n">
-        <v>191.21</v>
+        <v>182.51</v>
       </c>
       <c r="T2" t="n">
-        <v>219.06</v>
+        <v>204.93</v>
       </c>
       <c r="U2" t="n">
-        <v>258.15</v>
+        <v>246.34</v>
       </c>
       <c r="V2" t="n">
-        <v>268.39</v>
+        <v>285.33</v>
       </c>
       <c r="W2" t="n">
-        <v>262.64</v>
+        <v>282.87</v>
       </c>
       <c r="X2" t="n">
-        <v>220.83</v>
+        <v>230.22</v>
       </c>
       <c r="Y2" t="n">
-        <v>212.41</v>
+        <v>214.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>197.97</v>
+        <v>206.68</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>241.07</v>
+        <v>253.16</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>265.52</v>
+        <v>284.1</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>18h-20h</t>
+          <t>8h-10h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>238.6</v>
+        <v>244.1</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2h-17h</t>
+          <t>0h-18h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,110 +647,110 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B2" t="n">
-        <v>205.91</v>
+        <v>223.94</v>
       </c>
       <c r="C2" t="n">
-        <v>200.04</v>
+        <v>209.85</v>
       </c>
       <c r="D2" t="n">
-        <v>195.41</v>
+        <v>203.22</v>
       </c>
       <c r="E2" t="n">
-        <v>190.77</v>
+        <v>198.89</v>
       </c>
       <c r="F2" t="n">
-        <v>189.6</v>
+        <v>194.29</v>
       </c>
       <c r="G2" t="n">
-        <v>189.79</v>
+        <v>193.58</v>
       </c>
       <c r="H2" t="n">
-        <v>208.36</v>
+        <v>200.83</v>
       </c>
       <c r="I2" t="n">
-        <v>236.58</v>
+        <v>237.83</v>
       </c>
       <c r="J2" t="n">
-        <v>245.09</v>
+        <v>240.07</v>
       </c>
       <c r="K2" t="n">
-        <v>243.11</v>
+        <v>223.92</v>
       </c>
       <c r="L2" t="n">
-        <v>202.13</v>
+        <v>191.32</v>
       </c>
       <c r="M2" t="n">
-        <v>187.4</v>
+        <v>157.23</v>
       </c>
       <c r="N2" t="n">
-        <v>170.02</v>
+        <v>137.84</v>
       </c>
       <c r="O2" t="n">
-        <v>163.33</v>
+        <v>134.02</v>
       </c>
       <c r="P2" t="n">
-        <v>151.58</v>
+        <v>109.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>164.5</v>
+        <v>86.33</v>
       </c>
       <c r="R2" t="n">
-        <v>170.21</v>
+        <v>90.42</v>
       </c>
       <c r="S2" t="n">
-        <v>182.51</v>
+        <v>137.68</v>
       </c>
       <c r="T2" t="n">
-        <v>204.93</v>
+        <v>180.61</v>
       </c>
       <c r="U2" t="n">
-        <v>246.34</v>
+        <v>227.05</v>
       </c>
       <c r="V2" t="n">
-        <v>285.33</v>
+        <v>216.52</v>
       </c>
       <c r="W2" t="n">
-        <v>282.87</v>
+        <v>205.06</v>
       </c>
       <c r="X2" t="n">
-        <v>230.22</v>
+        <v>200.16</v>
       </c>
       <c r="Y2" t="n">
-        <v>214.21</v>
+        <v>177.68</v>
       </c>
       <c r="Z2" t="n">
-        <v>206.68</v>
+        <v>182.41</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>20h-24h</t>
+          <t>0h-4h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>253.16</v>
+        <v>208.98</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>20h-22h</t>
+          <t>8h-10h</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>284.1</v>
+        <v>232</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8h-10h</t>
+          <t>6h-8h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>244.1</v>
+        <v>219.33</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0h-18h</t>
+          <t>11h-23h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,110 +647,110 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2" t="n">
-        <v>223.94</v>
+        <v>197.08</v>
       </c>
       <c r="C2" t="n">
-        <v>209.85</v>
+        <v>179.63</v>
       </c>
       <c r="D2" t="n">
-        <v>203.22</v>
+        <v>157.26</v>
       </c>
       <c r="E2" t="n">
-        <v>198.89</v>
+        <v>136.38</v>
       </c>
       <c r="F2" t="n">
-        <v>194.29</v>
+        <v>129.75</v>
       </c>
       <c r="G2" t="n">
-        <v>193.58</v>
+        <v>129.44</v>
       </c>
       <c r="H2" t="n">
-        <v>200.83</v>
+        <v>134.17</v>
       </c>
       <c r="I2" t="n">
-        <v>237.83</v>
+        <v>168.75</v>
       </c>
       <c r="J2" t="n">
-        <v>240.07</v>
+        <v>195.52</v>
       </c>
       <c r="K2" t="n">
-        <v>223.92</v>
+        <v>130.29</v>
       </c>
       <c r="L2" t="n">
-        <v>191.32</v>
+        <v>16.4</v>
       </c>
       <c r="M2" t="n">
-        <v>157.23</v>
+        <v>0.13</v>
       </c>
       <c r="N2" t="n">
-        <v>137.84</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>134.02</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>109.4</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>86.33</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>90.42</v>
+        <v>0.11</v>
       </c>
       <c r="S2" t="n">
-        <v>137.68</v>
+        <v>1.78</v>
       </c>
       <c r="T2" t="n">
-        <v>180.61</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>227.05</v>
+        <v>176.47</v>
       </c>
       <c r="V2" t="n">
-        <v>216.52</v>
+        <v>198.8</v>
       </c>
       <c r="W2" t="n">
-        <v>205.06</v>
+        <v>186.63</v>
       </c>
       <c r="X2" t="n">
-        <v>200.16</v>
+        <v>177.68</v>
       </c>
       <c r="Y2" t="n">
-        <v>177.68</v>
+        <v>159.69</v>
       </c>
       <c r="Z2" t="n">
-        <v>182.41</v>
+        <v>106.9</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0h-4h</t>
+          <t>20h-24h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>208.98</v>
+        <v>180.7</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>8h-10h</t>
+          <t>20h-22h</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>232</v>
+        <v>192.72</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6h-8h</t>
+          <t>0h-2h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>219.33</v>
+        <v>188.36</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11h-23h</t>
+          <t>10h-18h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,43 +647,43 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2" t="n">
-        <v>197.08</v>
+        <v>156.83</v>
       </c>
       <c r="C2" t="n">
-        <v>179.63</v>
+        <v>133.59</v>
       </c>
       <c r="D2" t="n">
-        <v>157.26</v>
+        <v>129.13</v>
       </c>
       <c r="E2" t="n">
-        <v>136.38</v>
+        <v>137.31</v>
       </c>
       <c r="F2" t="n">
-        <v>129.75</v>
+        <v>141.59</v>
       </c>
       <c r="G2" t="n">
-        <v>129.44</v>
+        <v>150.14</v>
       </c>
       <c r="H2" t="n">
-        <v>134.17</v>
+        <v>158.53</v>
       </c>
       <c r="I2" t="n">
-        <v>168.75</v>
+        <v>170.73</v>
       </c>
       <c r="J2" t="n">
-        <v>195.52</v>
+        <v>174.88</v>
       </c>
       <c r="K2" t="n">
-        <v>130.29</v>
+        <v>123.57</v>
       </c>
       <c r="L2" t="n">
-        <v>16.4</v>
+        <v>20.07</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -695,34 +695,34 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="R2" t="n">
-        <v>0.11</v>
+        <v>6.99</v>
       </c>
       <c r="S2" t="n">
-        <v>1.78</v>
+        <v>36.68</v>
       </c>
       <c r="T2" t="n">
-        <v>89.56999999999999</v>
+        <v>113.74</v>
       </c>
       <c r="U2" t="n">
-        <v>176.47</v>
+        <v>192.33</v>
       </c>
       <c r="V2" t="n">
-        <v>198.8</v>
+        <v>198.34</v>
       </c>
       <c r="W2" t="n">
-        <v>186.63</v>
+        <v>192.67</v>
       </c>
       <c r="X2" t="n">
-        <v>177.68</v>
+        <v>188.31</v>
       </c>
       <c r="Y2" t="n">
-        <v>159.69</v>
+        <v>185.93</v>
       </c>
       <c r="Z2" t="n">
-        <v>106.9</v>
+        <v>108.84</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>180.7</v>
+        <v>191.31</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>192.72</v>
+        <v>195.5</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0h-2h</t>
+          <t>22h-24h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>188.36</v>
+        <v>187.12</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-18h</t>
+          <t>10h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,46 +647,46 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B2" t="n">
-        <v>156.83</v>
+        <v>192.89</v>
       </c>
       <c r="C2" t="n">
-        <v>133.59</v>
+        <v>189.99</v>
       </c>
       <c r="D2" t="n">
-        <v>129.13</v>
+        <v>190.17</v>
       </c>
       <c r="E2" t="n">
-        <v>137.31</v>
+        <v>190.72</v>
       </c>
       <c r="F2" t="n">
-        <v>141.59</v>
+        <v>198.05</v>
       </c>
       <c r="G2" t="n">
-        <v>150.14</v>
+        <v>199.76</v>
       </c>
       <c r="H2" t="n">
-        <v>158.53</v>
+        <v>199.63</v>
       </c>
       <c r="I2" t="n">
-        <v>170.73</v>
+        <v>195.85</v>
       </c>
       <c r="J2" t="n">
-        <v>174.88</v>
+        <v>202.38</v>
       </c>
       <c r="K2" t="n">
-        <v>123.57</v>
+        <v>126.57</v>
       </c>
       <c r="L2" t="n">
-        <v>20.07</v>
+        <v>45.95</v>
       </c>
       <c r="M2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.03</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -695,34 +695,34 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>6.99</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>36.68</v>
+        <v>29.06</v>
       </c>
       <c r="T2" t="n">
-        <v>113.74</v>
+        <v>137.19</v>
       </c>
       <c r="U2" t="n">
-        <v>192.33</v>
+        <v>200.53</v>
       </c>
       <c r="V2" t="n">
-        <v>198.34</v>
+        <v>218.87</v>
       </c>
       <c r="W2" t="n">
-        <v>192.67</v>
+        <v>215.3</v>
       </c>
       <c r="X2" t="n">
-        <v>188.31</v>
+        <v>201.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>185.93</v>
+        <v>204.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>108.84</v>
+        <v>130.83</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>191.31</v>
+        <v>210.04</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>195.5</v>
+        <v>217.08</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -746,11 +746,11 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>187.12</v>
+        <v>203</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-17h</t>
+          <t>9h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B2" t="n">
-        <v>192.89</v>
+        <v>200.25</v>
       </c>
       <c r="C2" t="n">
-        <v>189.99</v>
+        <v>199.86</v>
       </c>
       <c r="D2" t="n">
-        <v>190.17</v>
+        <v>198.74</v>
       </c>
       <c r="E2" t="n">
-        <v>190.72</v>
+        <v>197.83</v>
       </c>
       <c r="F2" t="n">
-        <v>198.05</v>
+        <v>197.69</v>
       </c>
       <c r="G2" t="n">
-        <v>199.76</v>
+        <v>197.22</v>
       </c>
       <c r="H2" t="n">
-        <v>199.63</v>
+        <v>197.55</v>
       </c>
       <c r="I2" t="n">
-        <v>195.85</v>
+        <v>198.57</v>
       </c>
       <c r="J2" t="n">
-        <v>202.38</v>
+        <v>198.79</v>
       </c>
       <c r="K2" t="n">
-        <v>126.57</v>
+        <v>141.93</v>
       </c>
       <c r="L2" t="n">
-        <v>45.95</v>
+        <v>83.94</v>
       </c>
       <c r="M2" t="n">
-        <v>0.89</v>
+        <v>26.66</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03</v>
+        <v>1.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>29.06</v>
+        <v>66.55</v>
       </c>
       <c r="T2" t="n">
-        <v>137.19</v>
+        <v>178.46</v>
       </c>
       <c r="U2" t="n">
-        <v>200.53</v>
+        <v>234.79</v>
       </c>
       <c r="V2" t="n">
-        <v>218.87</v>
+        <v>234</v>
       </c>
       <c r="W2" t="n">
-        <v>215.3</v>
+        <v>223.38</v>
       </c>
       <c r="X2" t="n">
-        <v>201.9</v>
+        <v>209.49</v>
       </c>
       <c r="Y2" t="n">
-        <v>204.09</v>
+        <v>205.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>130.83</v>
+        <v>141.49</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>210.04</v>
+        <v>217.99</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>217.08</v>
+        <v>228.69</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -746,11 +746,11 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>203</v>
+        <v>207.29</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9h-17h</t>
+          <t>10h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B2" t="n">
-        <v>200.25</v>
+        <v>207.66</v>
       </c>
       <c r="C2" t="n">
-        <v>199.86</v>
+        <v>208.83</v>
       </c>
       <c r="D2" t="n">
-        <v>198.74</v>
+        <v>199.64</v>
       </c>
       <c r="E2" t="n">
-        <v>197.83</v>
+        <v>197.02</v>
       </c>
       <c r="F2" t="n">
-        <v>197.69</v>
+        <v>197.47</v>
       </c>
       <c r="G2" t="n">
-        <v>197.22</v>
+        <v>185.55</v>
       </c>
       <c r="H2" t="n">
-        <v>197.55</v>
+        <v>206.53</v>
       </c>
       <c r="I2" t="n">
-        <v>198.57</v>
+        <v>241.29</v>
       </c>
       <c r="J2" t="n">
-        <v>198.79</v>
+        <v>246.78</v>
       </c>
       <c r="K2" t="n">
-        <v>141.93</v>
+        <v>214.27</v>
       </c>
       <c r="L2" t="n">
-        <v>83.94</v>
+        <v>184.13</v>
       </c>
       <c r="M2" t="n">
-        <v>26.66</v>
+        <v>146.23</v>
       </c>
       <c r="N2" t="n">
-        <v>1.2</v>
+        <v>97.75</v>
       </c>
       <c r="O2" t="n">
-        <v>1.07</v>
+        <v>72.78</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>54.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.52</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>1.16</v>
+        <v>96.75</v>
       </c>
       <c r="S2" t="n">
-        <v>66.55</v>
+        <v>150.64</v>
       </c>
       <c r="T2" t="n">
-        <v>178.46</v>
+        <v>199.08</v>
       </c>
       <c r="U2" t="n">
-        <v>234.79</v>
+        <v>243.35</v>
       </c>
       <c r="V2" t="n">
-        <v>234</v>
+        <v>256.11</v>
       </c>
       <c r="W2" t="n">
-        <v>223.38</v>
+        <v>266.74</v>
       </c>
       <c r="X2" t="n">
-        <v>209.49</v>
+        <v>256.73</v>
       </c>
       <c r="Y2" t="n">
-        <v>205.09</v>
+        <v>239.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>141.49</v>
+        <v>184.88</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>217.99</v>
+        <v>254.72</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>228.69</v>
+        <v>261.42</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>207.29</v>
+        <v>248.02</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2" t="n">
-        <v>207.66</v>
+        <v>216.5</v>
       </c>
       <c r="C2" t="n">
-        <v>208.83</v>
+        <v>201.27</v>
       </c>
       <c r="D2" t="n">
-        <v>199.64</v>
+        <v>199.67</v>
       </c>
       <c r="E2" t="n">
-        <v>197.02</v>
+        <v>201.5</v>
       </c>
       <c r="F2" t="n">
-        <v>197.47</v>
+        <v>200.63</v>
       </c>
       <c r="G2" t="n">
-        <v>185.55</v>
+        <v>205.3</v>
       </c>
       <c r="H2" t="n">
-        <v>206.53</v>
+        <v>222.63</v>
       </c>
       <c r="I2" t="n">
-        <v>241.29</v>
+        <v>234.96</v>
       </c>
       <c r="J2" t="n">
-        <v>246.78</v>
+        <v>254.83</v>
       </c>
       <c r="K2" t="n">
-        <v>214.27</v>
+        <v>213.73</v>
       </c>
       <c r="L2" t="n">
-        <v>184.13</v>
+        <v>160.78</v>
       </c>
       <c r="M2" t="n">
-        <v>146.23</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>97.75</v>
+        <v>59.82</v>
       </c>
       <c r="O2" t="n">
-        <v>72.78</v>
+        <v>39.25</v>
       </c>
       <c r="P2" t="n">
-        <v>54.55</v>
+        <v>33.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>68.01000000000001</v>
+        <v>29.15</v>
       </c>
       <c r="R2" t="n">
-        <v>96.75</v>
+        <v>45.84</v>
       </c>
       <c r="S2" t="n">
-        <v>150.64</v>
+        <v>109.94</v>
       </c>
       <c r="T2" t="n">
-        <v>199.08</v>
+        <v>193.14</v>
       </c>
       <c r="U2" t="n">
-        <v>243.35</v>
+        <v>231.85</v>
       </c>
       <c r="V2" t="n">
-        <v>256.11</v>
+        <v>260.62</v>
       </c>
       <c r="W2" t="n">
-        <v>266.74</v>
+        <v>230.2</v>
       </c>
       <c r="X2" t="n">
-        <v>256.73</v>
+        <v>220.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>239.3</v>
+        <v>197.57</v>
       </c>
       <c r="Z2" t="n">
-        <v>184.88</v>
+        <v>168.83</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>254.72</v>
+        <v>227.26</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,15 +738,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>261.42</v>
+        <v>245.41</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22h-24h</t>
+          <t>8h-10h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>248.02</v>
+        <v>234.28</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2" t="n">
-        <v>216.5</v>
+        <v>207.49</v>
       </c>
       <c r="C2" t="n">
-        <v>201.27</v>
+        <v>201.2</v>
       </c>
       <c r="D2" t="n">
-        <v>199.67</v>
+        <v>193.23</v>
       </c>
       <c r="E2" t="n">
-        <v>201.5</v>
+        <v>196</v>
       </c>
       <c r="F2" t="n">
-        <v>200.63</v>
+        <v>204.14</v>
       </c>
       <c r="G2" t="n">
-        <v>205.3</v>
+        <v>207.46</v>
       </c>
       <c r="H2" t="n">
-        <v>222.63</v>
+        <v>213.92</v>
       </c>
       <c r="I2" t="n">
-        <v>234.96</v>
+        <v>249.75</v>
       </c>
       <c r="J2" t="n">
-        <v>254.83</v>
+        <v>282.23</v>
       </c>
       <c r="K2" t="n">
-        <v>213.73</v>
+        <v>243.54</v>
       </c>
       <c r="L2" t="n">
-        <v>160.78</v>
+        <v>180.16</v>
       </c>
       <c r="M2" t="n">
-        <v>88.76000000000001</v>
+        <v>93.19</v>
       </c>
       <c r="N2" t="n">
-        <v>59.82</v>
+        <v>60.19</v>
       </c>
       <c r="O2" t="n">
-        <v>39.25</v>
+        <v>57.8</v>
       </c>
       <c r="P2" t="n">
-        <v>33.3</v>
+        <v>57.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>29.15</v>
+        <v>57.8</v>
       </c>
       <c r="R2" t="n">
-        <v>45.84</v>
+        <v>86.38</v>
       </c>
       <c r="S2" t="n">
-        <v>109.94</v>
+        <v>149.11</v>
       </c>
       <c r="T2" t="n">
-        <v>193.14</v>
+        <v>237.69</v>
       </c>
       <c r="U2" t="n">
-        <v>231.85</v>
+        <v>288.34</v>
       </c>
       <c r="V2" t="n">
-        <v>260.62</v>
+        <v>293.39</v>
       </c>
       <c r="W2" t="n">
-        <v>230.2</v>
+        <v>254.19</v>
       </c>
       <c r="X2" t="n">
-        <v>220.65</v>
+        <v>233.69</v>
       </c>
       <c r="Y2" t="n">
-        <v>197.57</v>
+        <v>226.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>168.83</v>
+        <v>186.45</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>227.26</v>
+        <v>251.84</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,15 +738,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>245.41</v>
+        <v>273.79</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8h-10h</t>
+          <t>18h-20h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>234.28</v>
+        <v>263.02</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B2" t="n">
-        <v>207.49</v>
+        <v>223.72</v>
       </c>
       <c r="C2" t="n">
-        <v>201.2</v>
+        <v>214.96</v>
       </c>
       <c r="D2" t="n">
-        <v>193.23</v>
+        <v>207.68</v>
       </c>
       <c r="E2" t="n">
-        <v>196</v>
+        <v>202.03</v>
       </c>
       <c r="F2" t="n">
-        <v>204.14</v>
+        <v>199.74</v>
       </c>
       <c r="G2" t="n">
-        <v>207.46</v>
+        <v>206.23</v>
       </c>
       <c r="H2" t="n">
-        <v>213.92</v>
+        <v>222.44</v>
       </c>
       <c r="I2" t="n">
-        <v>249.75</v>
+        <v>245.83</v>
       </c>
       <c r="J2" t="n">
-        <v>282.23</v>
+        <v>261.14</v>
       </c>
       <c r="K2" t="n">
-        <v>243.54</v>
+        <v>227.86</v>
       </c>
       <c r="L2" t="n">
-        <v>180.16</v>
+        <v>187.06</v>
       </c>
       <c r="M2" t="n">
-        <v>93.19</v>
+        <v>113.4</v>
       </c>
       <c r="N2" t="n">
-        <v>60.19</v>
+        <v>87.27</v>
       </c>
       <c r="O2" t="n">
-        <v>57.8</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>57.72</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>57.8</v>
+        <v>85.08</v>
       </c>
       <c r="R2" t="n">
-        <v>86.38</v>
+        <v>117.15</v>
       </c>
       <c r="S2" t="n">
-        <v>149.11</v>
+        <v>182.25</v>
       </c>
       <c r="T2" t="n">
-        <v>237.69</v>
+        <v>235.43</v>
       </c>
       <c r="U2" t="n">
-        <v>288.34</v>
+        <v>277.19</v>
       </c>
       <c r="V2" t="n">
-        <v>293.39</v>
+        <v>292.99</v>
       </c>
       <c r="W2" t="n">
-        <v>254.19</v>
+        <v>255.27</v>
       </c>
       <c r="X2" t="n">
-        <v>233.69</v>
+        <v>232.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>226.08</v>
+        <v>225.37</v>
       </c>
       <c r="Z2" t="n">
-        <v>186.45</v>
+        <v>193.61</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>251.84</v>
+        <v>251.48</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>273.79</v>
+        <v>274.13</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>263.02</v>
+        <v>256.31</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B2" t="n">
-        <v>223.72</v>
+        <v>220.94</v>
       </c>
       <c r="C2" t="n">
-        <v>214.96</v>
+        <v>209.44</v>
       </c>
       <c r="D2" t="n">
-        <v>207.68</v>
+        <v>202.71</v>
       </c>
       <c r="E2" t="n">
-        <v>202.03</v>
+        <v>199.02</v>
       </c>
       <c r="F2" t="n">
-        <v>199.74</v>
+        <v>199.12</v>
       </c>
       <c r="G2" t="n">
-        <v>206.23</v>
+        <v>204.02</v>
       </c>
       <c r="H2" t="n">
-        <v>222.44</v>
+        <v>226.49</v>
       </c>
       <c r="I2" t="n">
-        <v>245.83</v>
+        <v>254.11</v>
       </c>
       <c r="J2" t="n">
-        <v>261.14</v>
+        <v>269.86</v>
       </c>
       <c r="K2" t="n">
-        <v>227.86</v>
+        <v>256.72</v>
       </c>
       <c r="L2" t="n">
-        <v>187.06</v>
+        <v>210.31</v>
       </c>
       <c r="M2" t="n">
-        <v>113.4</v>
+        <v>151.89</v>
       </c>
       <c r="N2" t="n">
-        <v>87.27</v>
+        <v>144.04</v>
       </c>
       <c r="O2" t="n">
-        <v>68.23999999999999</v>
+        <v>105.5</v>
       </c>
       <c r="P2" t="n">
-        <v>76.01000000000001</v>
+        <v>102.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>85.08</v>
+        <v>111.61</v>
       </c>
       <c r="R2" t="n">
-        <v>117.15</v>
+        <v>148.83</v>
       </c>
       <c r="S2" t="n">
-        <v>182.25</v>
+        <v>174.8</v>
       </c>
       <c r="T2" t="n">
-        <v>235.43</v>
+        <v>227.27</v>
       </c>
       <c r="U2" t="n">
-        <v>277.19</v>
+        <v>264.64</v>
       </c>
       <c r="V2" t="n">
-        <v>292.99</v>
+        <v>254.69</v>
       </c>
       <c r="W2" t="n">
-        <v>255.27</v>
+        <v>237.61</v>
       </c>
       <c r="X2" t="n">
-        <v>232.3</v>
+        <v>212.46</v>
       </c>
       <c r="Y2" t="n">
-        <v>225.37</v>
+        <v>196.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>193.61</v>
+        <v>199.38</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,27 +730,27 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>251.48</v>
+        <v>225.25</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>8h-10h</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>263.29</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>20h-22h</t>
         </is>
       </c>
-      <c r="AD2" t="n">
-        <v>274.13</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>18h-20h</t>
-        </is>
-      </c>
       <c r="AF2" t="n">
-        <v>256.31</v>
+        <v>246.15</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-17h</t>
+          <t>3h-23h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,110 +647,110 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B2" t="n">
-        <v>220.94</v>
+        <v>204.1</v>
       </c>
       <c r="C2" t="n">
-        <v>209.44</v>
+        <v>188.28</v>
       </c>
       <c r="D2" t="n">
-        <v>202.71</v>
+        <v>171.89</v>
       </c>
       <c r="E2" t="n">
-        <v>199.02</v>
+        <v>148.26</v>
       </c>
       <c r="F2" t="n">
-        <v>199.12</v>
+        <v>137.7</v>
       </c>
       <c r="G2" t="n">
-        <v>204.02</v>
+        <v>129.67</v>
       </c>
       <c r="H2" t="n">
-        <v>226.49</v>
+        <v>150.77</v>
       </c>
       <c r="I2" t="n">
-        <v>254.11</v>
+        <v>171.27</v>
       </c>
       <c r="J2" t="n">
-        <v>269.86</v>
+        <v>191.39</v>
       </c>
       <c r="K2" t="n">
-        <v>256.72</v>
+        <v>133.73</v>
       </c>
       <c r="L2" t="n">
-        <v>210.31</v>
+        <v>64.23</v>
       </c>
       <c r="M2" t="n">
-        <v>151.89</v>
+        <v>2.49</v>
       </c>
       <c r="N2" t="n">
-        <v>144.04</v>
+        <v>1.03</v>
       </c>
       <c r="O2" t="n">
-        <v>105.5</v>
+        <v>1.07</v>
       </c>
       <c r="P2" t="n">
-        <v>102.75</v>
+        <v>1.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>111.61</v>
+        <v>1.07</v>
       </c>
       <c r="R2" t="n">
-        <v>148.83</v>
+        <v>3.83</v>
       </c>
       <c r="S2" t="n">
-        <v>174.8</v>
+        <v>49.64</v>
       </c>
       <c r="T2" t="n">
-        <v>227.27</v>
+        <v>110.97</v>
       </c>
       <c r="U2" t="n">
-        <v>264.64</v>
+        <v>143.33</v>
       </c>
       <c r="V2" t="n">
-        <v>254.69</v>
+        <v>146.21</v>
       </c>
       <c r="W2" t="n">
-        <v>237.61</v>
+        <v>151.07</v>
       </c>
       <c r="X2" t="n">
-        <v>212.46</v>
+        <v>142.42</v>
       </c>
       <c r="Y2" t="n">
-        <v>196.25</v>
+        <v>126.23</v>
       </c>
       <c r="Z2" t="n">
-        <v>199.38</v>
+        <v>107.16</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>20h-24h</t>
+          <t>0h-4h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>225.25</v>
+        <v>178.13</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>0h-2h</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>196.19</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>8h-10h</t>
         </is>
       </c>
-      <c r="AD2" t="n">
-        <v>263.29</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>20h-22h</t>
-        </is>
-      </c>
       <c r="AF2" t="n">
-        <v>246.15</v>
+        <v>162.56</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3h-23h</t>
+          <t>10h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,110 +647,110 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B2" t="n">
-        <v>204.1</v>
+        <v>131.11</v>
       </c>
       <c r="C2" t="n">
-        <v>188.28</v>
+        <v>123.6</v>
       </c>
       <c r="D2" t="n">
-        <v>171.89</v>
+        <v>103.69</v>
       </c>
       <c r="E2" t="n">
-        <v>148.26</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>137.7</v>
+        <v>70.11</v>
       </c>
       <c r="G2" t="n">
-        <v>129.67</v>
+        <v>67.81</v>
       </c>
       <c r="H2" t="n">
-        <v>150.77</v>
+        <v>92.39</v>
       </c>
       <c r="I2" t="n">
-        <v>171.27</v>
+        <v>93.41</v>
       </c>
       <c r="J2" t="n">
-        <v>191.39</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>133.73</v>
+        <v>55.22</v>
       </c>
       <c r="L2" t="n">
-        <v>64.23</v>
+        <v>3.39</v>
       </c>
       <c r="M2" t="n">
-        <v>2.49</v>
+        <v>0.34</v>
       </c>
       <c r="N2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.83</v>
+        <v>0.31</v>
       </c>
       <c r="S2" t="n">
-        <v>49.64</v>
+        <v>2.69</v>
       </c>
       <c r="T2" t="n">
-        <v>110.97</v>
+        <v>75.03</v>
       </c>
       <c r="U2" t="n">
-        <v>143.33</v>
+        <v>155.12</v>
       </c>
       <c r="V2" t="n">
-        <v>146.21</v>
+        <v>182.53</v>
       </c>
       <c r="W2" t="n">
-        <v>151.07</v>
+        <v>178.69</v>
       </c>
       <c r="X2" t="n">
-        <v>142.42</v>
+        <v>169.54</v>
       </c>
       <c r="Y2" t="n">
-        <v>126.23</v>
+        <v>151.63</v>
       </c>
       <c r="Z2" t="n">
-        <v>107.16</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0h-4h</t>
+          <t>20h-24h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>178.13</v>
+        <v>170.6</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0h-2h</t>
+          <t>20h-22h</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>196.19</v>
+        <v>180.61</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8h-10h</t>
+          <t>22h-24h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>162.56</v>
+        <v>160.58</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-17h</t>
+          <t>3h-18h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B2" t="n">
-        <v>131.11</v>
+        <v>176.08</v>
       </c>
       <c r="C2" t="n">
-        <v>123.6</v>
+        <v>170.46</v>
       </c>
       <c r="D2" t="n">
-        <v>103.69</v>
+        <v>168.87</v>
       </c>
       <c r="E2" t="n">
-        <v>74.90000000000001</v>
+        <v>170.34</v>
       </c>
       <c r="F2" t="n">
-        <v>70.11</v>
+        <v>170.98</v>
       </c>
       <c r="G2" t="n">
-        <v>67.81</v>
+        <v>185.14</v>
       </c>
       <c r="H2" t="n">
-        <v>92.39</v>
+        <v>214.52</v>
       </c>
       <c r="I2" t="n">
-        <v>93.41</v>
+        <v>229.63</v>
       </c>
       <c r="J2" t="n">
-        <v>99.34999999999999</v>
+        <v>267.47</v>
       </c>
       <c r="K2" t="n">
-        <v>55.22</v>
+        <v>249.19</v>
       </c>
       <c r="L2" t="n">
-        <v>3.39</v>
+        <v>225.75</v>
       </c>
       <c r="M2" t="n">
-        <v>0.34</v>
+        <v>184.38</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>168.99</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>170.46</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>176.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>183.75</v>
       </c>
       <c r="R2" t="n">
-        <v>0.31</v>
+        <v>206.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.69</v>
+        <v>245.7</v>
       </c>
       <c r="T2" t="n">
-        <v>75.03</v>
+        <v>272.22</v>
       </c>
       <c r="U2" t="n">
-        <v>155.12</v>
+        <v>283.57</v>
       </c>
       <c r="V2" t="n">
-        <v>182.53</v>
+        <v>309.14</v>
       </c>
       <c r="W2" t="n">
-        <v>178.69</v>
+        <v>299.83</v>
       </c>
       <c r="X2" t="n">
-        <v>169.54</v>
+        <v>242.89</v>
       </c>
       <c r="Y2" t="n">
-        <v>151.63</v>
+        <v>228</v>
       </c>
       <c r="Z2" t="n">
-        <v>76.29000000000001</v>
+        <v>216.66</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>170.6</v>
+        <v>269.96</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>180.61</v>
+        <v>304.48</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22h-24h</t>
+          <t>18h-20h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>160.58</v>
+        <v>277.9</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3h-18h</t>
+          <t>0h-16h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B2" t="n">
-        <v>176.08</v>
+        <v>229.5</v>
       </c>
       <c r="C2" t="n">
-        <v>170.46</v>
+        <v>223.54</v>
       </c>
       <c r="D2" t="n">
-        <v>168.87</v>
+        <v>222.89</v>
       </c>
       <c r="E2" t="n">
-        <v>170.34</v>
+        <v>221.26</v>
       </c>
       <c r="F2" t="n">
-        <v>170.98</v>
+        <v>220.92</v>
       </c>
       <c r="G2" t="n">
-        <v>185.14</v>
+        <v>220.38</v>
       </c>
       <c r="H2" t="n">
-        <v>214.52</v>
+        <v>220.12</v>
       </c>
       <c r="I2" t="n">
-        <v>229.63</v>
+        <v>233.31</v>
       </c>
       <c r="J2" t="n">
-        <v>267.47</v>
+        <v>254.22</v>
       </c>
       <c r="K2" t="n">
-        <v>249.19</v>
+        <v>239.58</v>
       </c>
       <c r="L2" t="n">
-        <v>225.75</v>
+        <v>217.37</v>
       </c>
       <c r="M2" t="n">
-        <v>184.38</v>
+        <v>157.19</v>
       </c>
       <c r="N2" t="n">
-        <v>168.99</v>
+        <v>134.81</v>
       </c>
       <c r="O2" t="n">
-        <v>170.46</v>
+        <v>111.19</v>
       </c>
       <c r="P2" t="n">
-        <v>176.08</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.75</v>
+        <v>61.66</v>
       </c>
       <c r="R2" t="n">
-        <v>206.49</v>
+        <v>85.94</v>
       </c>
       <c r="S2" t="n">
-        <v>245.7</v>
+        <v>142.85</v>
       </c>
       <c r="T2" t="n">
-        <v>272.22</v>
+        <v>228.82</v>
       </c>
       <c r="U2" t="n">
-        <v>283.57</v>
+        <v>271.4</v>
       </c>
       <c r="V2" t="n">
-        <v>309.14</v>
+        <v>259.03</v>
       </c>
       <c r="W2" t="n">
-        <v>299.83</v>
+        <v>229.79</v>
       </c>
       <c r="X2" t="n">
-        <v>242.89</v>
+        <v>216.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>228</v>
+        <v>201.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>216.66</v>
+        <v>195.52</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,27 +730,27 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>269.96</v>
+        <v>226.75</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>20h-22h</t>
+          <t>18h-20h</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>304.48</v>
+        <v>250.11</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>18h-20h</t>
+          <t>8h-10h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>277.9</v>
+        <v>246.9</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0h-16h</t>
+          <t>11h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B2" t="n">
-        <v>229.5</v>
+        <v>177.86</v>
       </c>
       <c r="C2" t="n">
-        <v>223.54</v>
+        <v>178.48</v>
       </c>
       <c r="D2" t="n">
-        <v>222.89</v>
+        <v>167.75</v>
       </c>
       <c r="E2" t="n">
-        <v>221.26</v>
+        <v>161.67</v>
       </c>
       <c r="F2" t="n">
-        <v>220.92</v>
+        <v>160.48</v>
       </c>
       <c r="G2" t="n">
-        <v>220.38</v>
+        <v>166.33</v>
       </c>
       <c r="H2" t="n">
-        <v>220.12</v>
+        <v>184.24</v>
       </c>
       <c r="I2" t="n">
-        <v>233.31</v>
+        <v>226.09</v>
       </c>
       <c r="J2" t="n">
-        <v>254.22</v>
+        <v>258.25</v>
       </c>
       <c r="K2" t="n">
-        <v>239.58</v>
+        <v>196.6</v>
       </c>
       <c r="L2" t="n">
-        <v>217.37</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>157.19</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>134.81</v>
+        <v>0.95</v>
       </c>
       <c r="O2" t="n">
-        <v>111.19</v>
+        <v>0.75</v>
       </c>
       <c r="P2" t="n">
-        <v>88.59999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>61.66</v>
+        <v>0.42</v>
       </c>
       <c r="R2" t="n">
-        <v>85.94</v>
+        <v>0.78</v>
       </c>
       <c r="S2" t="n">
-        <v>142.85</v>
+        <v>68.88</v>
       </c>
       <c r="T2" t="n">
-        <v>228.82</v>
+        <v>193.22</v>
       </c>
       <c r="U2" t="n">
-        <v>271.4</v>
+        <v>255.14</v>
       </c>
       <c r="V2" t="n">
-        <v>259.03</v>
+        <v>284.49</v>
       </c>
       <c r="W2" t="n">
-        <v>229.79</v>
+        <v>284.93</v>
       </c>
       <c r="X2" t="n">
-        <v>216.52</v>
+        <v>253.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>201.66</v>
+        <v>224.61</v>
       </c>
       <c r="Z2" t="n">
-        <v>195.52</v>
+        <v>146.97</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,27 +730,27 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>226.75</v>
+        <v>261.99</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>18h-20h</t>
+          <t>20h-22h</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>250.11</v>
+        <v>284.71</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8h-10h</t>
+          <t>22h-24h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>246.9</v>
+        <v>239.26</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11h-17h</t>
+          <t>10h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,106 +647,106 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B2" t="n">
-        <v>177.86</v>
+        <v>220.75</v>
       </c>
       <c r="C2" t="n">
-        <v>178.48</v>
+        <v>214.94</v>
       </c>
       <c r="D2" t="n">
-        <v>167.75</v>
+        <v>212.53</v>
       </c>
       <c r="E2" t="n">
-        <v>161.67</v>
+        <v>212.11</v>
       </c>
       <c r="F2" t="n">
-        <v>160.48</v>
+        <v>209.98</v>
       </c>
       <c r="G2" t="n">
-        <v>166.33</v>
+        <v>211.52</v>
       </c>
       <c r="H2" t="n">
-        <v>184.24</v>
+        <v>217.78</v>
       </c>
       <c r="I2" t="n">
-        <v>226.09</v>
+        <v>234.52</v>
       </c>
       <c r="J2" t="n">
-        <v>258.25</v>
+        <v>256.07</v>
       </c>
       <c r="K2" t="n">
-        <v>196.6</v>
+        <v>232.47</v>
       </c>
       <c r="L2" t="n">
-        <v>78.70999999999999</v>
+        <v>145.56</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>62.77</v>
       </c>
       <c r="N2" t="n">
-        <v>0.95</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>0.75</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="R2" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="S2" t="n">
-        <v>68.88</v>
+        <v>33.26</v>
       </c>
       <c r="T2" t="n">
-        <v>193.22</v>
+        <v>166.59</v>
       </c>
       <c r="U2" t="n">
-        <v>255.14</v>
+        <v>242.32</v>
       </c>
       <c r="V2" t="n">
-        <v>284.49</v>
+        <v>245.28</v>
       </c>
       <c r="W2" t="n">
-        <v>284.93</v>
+        <v>218.37</v>
       </c>
       <c r="X2" t="n">
-        <v>253.92</v>
+        <v>205.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>224.61</v>
+        <v>186.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>146.97</v>
+        <v>155.63</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>20h-24h</t>
+          <t>4h-8h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>261.99</v>
+        <v>218.45</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>8h-10h</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>244.27</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>20h-22h</t>
         </is>
       </c>
-      <c r="AD2" t="n">
-        <v>284.71</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>22h-24h</t>
-        </is>
-      </c>
       <c r="AF2" t="n">
-        <v>239.26</v>
+        <v>231.82</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,110 +647,110 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B2" t="n">
-        <v>220.75</v>
+        <v>140.63</v>
       </c>
       <c r="C2" t="n">
-        <v>214.94</v>
+        <v>122.53</v>
       </c>
       <c r="D2" t="n">
-        <v>212.53</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>212.11</v>
+        <v>93.39</v>
       </c>
       <c r="F2" t="n">
-        <v>209.98</v>
+        <v>90.08</v>
       </c>
       <c r="G2" t="n">
-        <v>211.52</v>
+        <v>99.61</v>
       </c>
       <c r="H2" t="n">
-        <v>217.78</v>
+        <v>132.57</v>
       </c>
       <c r="I2" t="n">
-        <v>234.52</v>
+        <v>174.82</v>
       </c>
       <c r="J2" t="n">
-        <v>256.07</v>
+        <v>192.36</v>
       </c>
       <c r="K2" t="n">
-        <v>232.47</v>
+        <v>163.88</v>
       </c>
       <c r="L2" t="n">
-        <v>145.56</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>62.77</v>
+        <v>16.67</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="R2" t="n">
-        <v>0.72</v>
+        <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>33.26</v>
+        <v>51.66</v>
       </c>
       <c r="T2" t="n">
-        <v>166.59</v>
+        <v>149.61</v>
       </c>
       <c r="U2" t="n">
-        <v>242.32</v>
+        <v>206.38</v>
       </c>
       <c r="V2" t="n">
-        <v>245.28</v>
+        <v>216.24</v>
       </c>
       <c r="W2" t="n">
-        <v>218.37</v>
+        <v>211.49</v>
       </c>
       <c r="X2" t="n">
-        <v>205.3</v>
+        <v>196.57</v>
       </c>
       <c r="Y2" t="n">
-        <v>186.24</v>
+        <v>192.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>155.63</v>
+        <v>110.09</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4h-8h</t>
+          <t>20h-24h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>218.45</v>
+        <v>204.1</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>8h-10h</t>
+          <t>20h-22h</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>244.27</v>
+        <v>213.86</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>20h-22h</t>
+          <t>22h-24h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>231.82</v>
+        <v>194.33</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-17h</t>
+          <t>2h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B2" t="n">
-        <v>140.63</v>
+        <v>203.88</v>
       </c>
       <c r="C2" t="n">
-        <v>122.53</v>
+        <v>201.21</v>
       </c>
       <c r="D2" t="n">
-        <v>96.04000000000001</v>
+        <v>200.96</v>
       </c>
       <c r="E2" t="n">
-        <v>93.39</v>
+        <v>200.96</v>
       </c>
       <c r="F2" t="n">
-        <v>90.08</v>
+        <v>200.73</v>
       </c>
       <c r="G2" t="n">
-        <v>99.61</v>
+        <v>199.85</v>
       </c>
       <c r="H2" t="n">
-        <v>132.57</v>
+        <v>200.35</v>
       </c>
       <c r="I2" t="n">
-        <v>174.82</v>
+        <v>202.22</v>
       </c>
       <c r="J2" t="n">
-        <v>192.36</v>
+        <v>212.61</v>
       </c>
       <c r="K2" t="n">
-        <v>163.88</v>
+        <v>168.52</v>
       </c>
       <c r="L2" t="n">
-        <v>89.40000000000001</v>
+        <v>62.73</v>
       </c>
       <c r="M2" t="n">
-        <v>16.67</v>
+        <v>1.32</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.74</v>
+        <v>-0.01</v>
       </c>
       <c r="R2" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>51.66</v>
+        <v>27.1</v>
       </c>
       <c r="T2" t="n">
-        <v>149.61</v>
+        <v>144.46</v>
       </c>
       <c r="U2" t="n">
-        <v>206.38</v>
+        <v>216.55</v>
       </c>
       <c r="V2" t="n">
-        <v>216.24</v>
+        <v>224.57</v>
       </c>
       <c r="W2" t="n">
-        <v>211.49</v>
+        <v>222.98</v>
       </c>
       <c r="X2" t="n">
-        <v>196.57</v>
+        <v>206.32</v>
       </c>
       <c r="Y2" t="n">
-        <v>192.09</v>
+        <v>195.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>110.09</v>
+        <v>137.19</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>204.1</v>
+        <v>212.3</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>213.86</v>
+        <v>223.77</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22h-24h</t>
+          <t>0h-2h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>194.33</v>
+        <v>202.54</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2h-17h</t>
+          <t>10h-17h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="B2" t="n">
-        <v>203.88</v>
+        <v>227.62</v>
       </c>
       <c r="C2" t="n">
-        <v>201.21</v>
+        <v>225.81</v>
       </c>
       <c r="D2" t="n">
-        <v>200.96</v>
+        <v>224.3</v>
       </c>
       <c r="E2" t="n">
-        <v>200.96</v>
+        <v>224.38</v>
       </c>
       <c r="F2" t="n">
-        <v>200.73</v>
+        <v>225.74</v>
       </c>
       <c r="G2" t="n">
-        <v>199.85</v>
+        <v>228.07</v>
       </c>
       <c r="H2" t="n">
-        <v>200.35</v>
+        <v>238.52</v>
       </c>
       <c r="I2" t="n">
-        <v>202.22</v>
+        <v>292.36</v>
       </c>
       <c r="J2" t="n">
-        <v>212.61</v>
+        <v>238.78</v>
       </c>
       <c r="K2" t="n">
-        <v>168.52</v>
+        <v>161.19</v>
       </c>
       <c r="L2" t="n">
-        <v>62.73</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>1.32</v>
+        <v>59.32</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>57.61</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>57.66</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>56.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.01</v>
+        <v>73.23</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>157.57</v>
       </c>
       <c r="S2" t="n">
-        <v>27.1</v>
+        <v>254.24</v>
       </c>
       <c r="T2" t="n">
-        <v>144.46</v>
+        <v>286.33</v>
       </c>
       <c r="U2" t="n">
-        <v>216.55</v>
+        <v>295.49</v>
       </c>
       <c r="V2" t="n">
-        <v>224.57</v>
+        <v>300</v>
       </c>
       <c r="W2" t="n">
-        <v>222.98</v>
+        <v>283.64</v>
       </c>
       <c r="X2" t="n">
-        <v>206.32</v>
+        <v>235.97</v>
       </c>
       <c r="Y2" t="n">
-        <v>195.32</v>
+        <v>227.54</v>
       </c>
       <c r="Z2" t="n">
-        <v>137.19</v>
+        <v>196.86</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>212.3</v>
+        <v>261.79</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>223.77</v>
+        <v>291.82</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0h-2h</t>
+          <t>18h-20h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>202.54</v>
+        <v>290.91</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10h-17h</t>
+          <t>9h-16h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,110 +647,110 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B2" t="n">
-        <v>227.62</v>
+        <v>222.77</v>
       </c>
       <c r="C2" t="n">
-        <v>225.81</v>
+        <v>216.91</v>
       </c>
       <c r="D2" t="n">
-        <v>224.3</v>
+        <v>209.78</v>
       </c>
       <c r="E2" t="n">
-        <v>224.38</v>
+        <v>210.2</v>
       </c>
       <c r="F2" t="n">
-        <v>225.74</v>
+        <v>219.53</v>
       </c>
       <c r="G2" t="n">
-        <v>228.07</v>
+        <v>221.43</v>
       </c>
       <c r="H2" t="n">
-        <v>238.52</v>
+        <v>233.39</v>
       </c>
       <c r="I2" t="n">
-        <v>292.36</v>
+        <v>246.08</v>
       </c>
       <c r="J2" t="n">
-        <v>238.78</v>
+        <v>239.02</v>
       </c>
       <c r="K2" t="n">
-        <v>161.19</v>
+        <v>206.44</v>
       </c>
       <c r="L2" t="n">
-        <v>92.81999999999999</v>
+        <v>141.37</v>
       </c>
       <c r="M2" t="n">
-        <v>59.32</v>
+        <v>127.04</v>
       </c>
       <c r="N2" t="n">
-        <v>57.61</v>
+        <v>116.62</v>
       </c>
       <c r="O2" t="n">
-        <v>57.66</v>
+        <v>106.12</v>
       </c>
       <c r="P2" t="n">
-        <v>56.54</v>
+        <v>113.31</v>
       </c>
       <c r="Q2" t="n">
-        <v>73.23</v>
+        <v>142.55</v>
       </c>
       <c r="R2" t="n">
-        <v>157.57</v>
+        <v>214.82</v>
       </c>
       <c r="S2" t="n">
-        <v>254.24</v>
+        <v>257.03</v>
       </c>
       <c r="T2" t="n">
-        <v>286.33</v>
+        <v>283.05</v>
       </c>
       <c r="U2" t="n">
-        <v>295.49</v>
+        <v>276.65</v>
       </c>
       <c r="V2" t="n">
-        <v>300</v>
+        <v>262.48</v>
       </c>
       <c r="W2" t="n">
-        <v>283.64</v>
+        <v>248</v>
       </c>
       <c r="X2" t="n">
-        <v>235.97</v>
+        <v>236.49</v>
       </c>
       <c r="Y2" t="n">
-        <v>227.54</v>
+        <v>223.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>196.86</v>
+        <v>207.26</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>20h-24h</t>
+          <t>16h-20h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>261.79</v>
+        <v>257.89</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>18h-20h</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>279.85</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>20h-22h</t>
         </is>
       </c>
-      <c r="AD2" t="n">
-        <v>291.82</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>18h-20h</t>
-        </is>
-      </c>
       <c r="AF2" t="n">
-        <v>290.91</v>
+        <v>255.24</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9h-16h</t>
+          <t>9h-15h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,90 +647,90 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B2" t="n">
-        <v>222.77</v>
+        <v>222.57</v>
       </c>
       <c r="C2" t="n">
-        <v>216.91</v>
+        <v>215.97</v>
       </c>
       <c r="D2" t="n">
-        <v>209.78</v>
+        <v>218.14</v>
       </c>
       <c r="E2" t="n">
-        <v>210.2</v>
+        <v>213.21</v>
       </c>
       <c r="F2" t="n">
-        <v>219.53</v>
+        <v>208.02</v>
       </c>
       <c r="G2" t="n">
-        <v>221.43</v>
+        <v>214.73</v>
       </c>
       <c r="H2" t="n">
-        <v>233.39</v>
+        <v>240.14</v>
       </c>
       <c r="I2" t="n">
-        <v>246.08</v>
+        <v>281.78</v>
       </c>
       <c r="J2" t="n">
-        <v>239.02</v>
+        <v>245.44</v>
       </c>
       <c r="K2" t="n">
-        <v>206.44</v>
+        <v>145.28</v>
       </c>
       <c r="L2" t="n">
-        <v>141.37</v>
+        <v>73.31</v>
       </c>
       <c r="M2" t="n">
-        <v>127.04</v>
+        <v>57.52</v>
       </c>
       <c r="N2" t="n">
-        <v>116.62</v>
+        <v>58.72</v>
       </c>
       <c r="O2" t="n">
-        <v>106.12</v>
+        <v>67.62</v>
       </c>
       <c r="P2" t="n">
-        <v>113.31</v>
+        <v>70.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>142.55</v>
+        <v>93.73</v>
       </c>
       <c r="R2" t="n">
-        <v>214.82</v>
+        <v>160.65</v>
       </c>
       <c r="S2" t="n">
-        <v>257.03</v>
+        <v>251.18</v>
       </c>
       <c r="T2" t="n">
-        <v>283.05</v>
+        <v>295.21</v>
       </c>
       <c r="U2" t="n">
-        <v>276.65</v>
+        <v>314.23</v>
       </c>
       <c r="V2" t="n">
-        <v>262.48</v>
+        <v>310.64</v>
       </c>
       <c r="W2" t="n">
-        <v>248</v>
+        <v>291.47</v>
       </c>
       <c r="X2" t="n">
-        <v>236.49</v>
+        <v>288.14</v>
       </c>
       <c r="Y2" t="n">
-        <v>223.25</v>
+        <v>272.51</v>
       </c>
       <c r="Z2" t="n">
-        <v>207.26</v>
+        <v>200.45</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>16h-20h</t>
+          <t>20h-24h</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>257.89</v>
+        <v>290.69</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>279.85</v>
+        <v>304.72</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -746,11 +746,11 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>255.24</v>
+        <v>301.06</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9h-15h</t>
+          <t>9h-16h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B2" t="n">
-        <v>222.57</v>
+        <v>244.22</v>
       </c>
       <c r="C2" t="n">
-        <v>215.97</v>
+        <v>237.34</v>
       </c>
       <c r="D2" t="n">
-        <v>218.14</v>
+        <v>232.41</v>
       </c>
       <c r="E2" t="n">
-        <v>213.21</v>
+        <v>229.35</v>
       </c>
       <c r="F2" t="n">
-        <v>208.02</v>
+        <v>229.69</v>
       </c>
       <c r="G2" t="n">
-        <v>214.73</v>
+        <v>238.34</v>
       </c>
       <c r="H2" t="n">
-        <v>240.14</v>
+        <v>267.71</v>
       </c>
       <c r="I2" t="n">
-        <v>281.78</v>
+        <v>298.71</v>
       </c>
       <c r="J2" t="n">
-        <v>245.44</v>
+        <v>276.02</v>
       </c>
       <c r="K2" t="n">
-        <v>145.28</v>
+        <v>231.92</v>
       </c>
       <c r="L2" t="n">
-        <v>73.31</v>
+        <v>149.79</v>
       </c>
       <c r="M2" t="n">
-        <v>57.52</v>
+        <v>123.82</v>
       </c>
       <c r="N2" t="n">
-        <v>58.72</v>
+        <v>117.85</v>
       </c>
       <c r="O2" t="n">
-        <v>67.62</v>
+        <v>124.1</v>
       </c>
       <c r="P2" t="n">
-        <v>70.56</v>
+        <v>128.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>93.73</v>
+        <v>139.07</v>
       </c>
       <c r="R2" t="n">
-        <v>160.65</v>
+        <v>214.74</v>
       </c>
       <c r="S2" t="n">
-        <v>251.18</v>
+        <v>300.5</v>
       </c>
       <c r="T2" t="n">
-        <v>295.21</v>
+        <v>317.03</v>
       </c>
       <c r="U2" t="n">
-        <v>314.23</v>
+        <v>346.1</v>
       </c>
       <c r="V2" t="n">
-        <v>310.64</v>
+        <v>358.05</v>
       </c>
       <c r="W2" t="n">
-        <v>291.47</v>
+        <v>352.58</v>
       </c>
       <c r="X2" t="n">
-        <v>288.14</v>
+        <v>306.27</v>
       </c>
       <c r="Y2" t="n">
-        <v>272.51</v>
+        <v>301.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>200.45</v>
+        <v>240.24</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,27 +730,27 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>290.69</v>
+        <v>329.64</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>20h-22h</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>18h-20h</t>
         </is>
       </c>
-      <c r="AD2" t="n">
-        <v>304.72</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>20h-22h</t>
-        </is>
-      </c>
       <c r="AF2" t="n">
-        <v>301.06</v>
+        <v>331.56</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9h-16h</t>
+          <t>1h-16h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B2" t="n">
-        <v>244.22</v>
+        <v>255.7</v>
       </c>
       <c r="C2" t="n">
-        <v>237.34</v>
+        <v>241.38</v>
       </c>
       <c r="D2" t="n">
-        <v>232.41</v>
+        <v>233.74</v>
       </c>
       <c r="E2" t="n">
-        <v>229.35</v>
+        <v>231.12</v>
       </c>
       <c r="F2" t="n">
-        <v>229.69</v>
+        <v>227.81</v>
       </c>
       <c r="G2" t="n">
-        <v>238.34</v>
+        <v>234.71</v>
       </c>
       <c r="H2" t="n">
-        <v>267.71</v>
+        <v>256.7</v>
       </c>
       <c r="I2" t="n">
-        <v>298.71</v>
+        <v>290.88</v>
       </c>
       <c r="J2" t="n">
-        <v>276.02</v>
+        <v>292.06</v>
       </c>
       <c r="K2" t="n">
-        <v>231.92</v>
+        <v>248.86</v>
       </c>
       <c r="L2" t="n">
-        <v>149.79</v>
+        <v>227.96</v>
       </c>
       <c r="M2" t="n">
-        <v>123.82</v>
+        <v>182.75</v>
       </c>
       <c r="N2" t="n">
-        <v>117.85</v>
+        <v>174.12</v>
       </c>
       <c r="O2" t="n">
-        <v>124.1</v>
+        <v>173.41</v>
       </c>
       <c r="P2" t="n">
-        <v>128.4</v>
+        <v>175.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>139.07</v>
+        <v>199.06</v>
       </c>
       <c r="R2" t="n">
-        <v>214.74</v>
+        <v>247.71</v>
       </c>
       <c r="S2" t="n">
-        <v>300.5</v>
+        <v>279.17</v>
       </c>
       <c r="T2" t="n">
-        <v>317.03</v>
+        <v>316.94</v>
       </c>
       <c r="U2" t="n">
-        <v>346.1</v>
+        <v>312.9</v>
       </c>
       <c r="V2" t="n">
-        <v>358.05</v>
+        <v>320.76</v>
       </c>
       <c r="W2" t="n">
-        <v>352.58</v>
+        <v>321.91</v>
       </c>
       <c r="X2" t="n">
-        <v>306.27</v>
+        <v>287.19</v>
       </c>
       <c r="Y2" t="n">
-        <v>301.66</v>
+        <v>250.72</v>
       </c>
       <c r="Z2" t="n">
-        <v>240.24</v>
+        <v>249.28</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>329.64</v>
+        <v>295.14</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>355.32</v>
+        <v>321.34</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>331.56</v>
+        <v>314.92</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="B2" t="n">
-        <v>255.7</v>
+        <v>264.14</v>
       </c>
       <c r="C2" t="n">
-        <v>241.38</v>
+        <v>266.66</v>
       </c>
       <c r="D2" t="n">
-        <v>233.74</v>
+        <v>266.68</v>
       </c>
       <c r="E2" t="n">
-        <v>231.12</v>
+        <v>265.32</v>
       </c>
       <c r="F2" t="n">
-        <v>227.81</v>
+        <v>261.97</v>
       </c>
       <c r="G2" t="n">
-        <v>234.71</v>
+        <v>255.44</v>
       </c>
       <c r="H2" t="n">
-        <v>256.7</v>
+        <v>250.93</v>
       </c>
       <c r="I2" t="n">
-        <v>290.88</v>
+        <v>256.47</v>
       </c>
       <c r="J2" t="n">
-        <v>292.06</v>
+        <v>253.37</v>
       </c>
       <c r="K2" t="n">
-        <v>248.86</v>
+        <v>175.02</v>
       </c>
       <c r="L2" t="n">
-        <v>227.96</v>
+        <v>104.07</v>
       </c>
       <c r="M2" t="n">
-        <v>182.75</v>
+        <v>62.19</v>
       </c>
       <c r="N2" t="n">
-        <v>174.12</v>
+        <v>57.76</v>
       </c>
       <c r="O2" t="n">
-        <v>173.41</v>
+        <v>57.98</v>
       </c>
       <c r="P2" t="n">
-        <v>175.05</v>
+        <v>57.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>199.06</v>
+        <v>63.22</v>
       </c>
       <c r="R2" t="n">
-        <v>247.71</v>
+        <v>149.25</v>
       </c>
       <c r="S2" t="n">
-        <v>279.17</v>
+        <v>254.72</v>
       </c>
       <c r="T2" t="n">
-        <v>316.94</v>
+        <v>300</v>
       </c>
       <c r="U2" t="n">
-        <v>312.9</v>
+        <v>298.31</v>
       </c>
       <c r="V2" t="n">
-        <v>320.76</v>
+        <v>291.53</v>
       </c>
       <c r="W2" t="n">
-        <v>321.91</v>
+        <v>276.73</v>
       </c>
       <c r="X2" t="n">
-        <v>287.19</v>
+        <v>266.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>250.72</v>
+        <v>259.52</v>
       </c>
       <c r="Z2" t="n">
-        <v>249.28</v>
+        <v>208.98</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,27 +730,27 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>295.14</v>
+        <v>273.53</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>18h-20h</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>299.15</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>20h-22h</t>
         </is>
       </c>
-      <c r="AD2" t="n">
-        <v>321.34</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>18h-20h</t>
-        </is>
-      </c>
       <c r="AF2" t="n">
-        <v>314.92</v>
+        <v>284.13</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1h-16h</t>
+          <t>9h-16h</t>
         </is>
       </c>
     </row>

--- a/output/spot_price_dailyHour_PT.xlsx
+++ b/output/spot_price_dailyHour_PT.xlsx
@@ -647,82 +647,82 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="B2" t="n">
-        <v>264.14</v>
+        <v>255.1</v>
       </c>
       <c r="C2" t="n">
-        <v>266.66</v>
+        <v>251.59</v>
       </c>
       <c r="D2" t="n">
-        <v>266.68</v>
+        <v>246.43</v>
       </c>
       <c r="E2" t="n">
-        <v>265.32</v>
+        <v>241.04</v>
       </c>
       <c r="F2" t="n">
-        <v>261.97</v>
+        <v>237.93</v>
       </c>
       <c r="G2" t="n">
-        <v>255.44</v>
+        <v>240.32</v>
       </c>
       <c r="H2" t="n">
-        <v>250.93</v>
+        <v>242.72</v>
       </c>
       <c r="I2" t="n">
-        <v>256.47</v>
+        <v>247.78</v>
       </c>
       <c r="J2" t="n">
-        <v>253.37</v>
+        <v>204.04</v>
       </c>
       <c r="K2" t="n">
-        <v>175.02</v>
+        <v>70.78</v>
       </c>
       <c r="L2" t="n">
-        <v>104.07</v>
+        <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>62.19</v>
+        <v>-0.02</v>
       </c>
       <c r="N2" t="n">
-        <v>57.76</v>
+        <v>-0.09</v>
       </c>
       <c r="O2" t="n">
-        <v>57.98</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>57.81</v>
+        <v>-0.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>63.22</v>
+        <v>-0.27</v>
       </c>
       <c r="R2" t="n">
-        <v>149.25</v>
+        <v>15.38</v>
       </c>
       <c r="S2" t="n">
-        <v>254.72</v>
+        <v>157.15</v>
       </c>
       <c r="T2" t="n">
-        <v>300</v>
+        <v>242.94</v>
       </c>
       <c r="U2" t="n">
-        <v>298.31</v>
+        <v>255.04</v>
       </c>
       <c r="V2" t="n">
-        <v>291.53</v>
+        <v>261.93</v>
       </c>
       <c r="W2" t="n">
-        <v>276.73</v>
+        <v>260.92</v>
       </c>
       <c r="X2" t="n">
-        <v>266.36</v>
+        <v>251.13</v>
       </c>
       <c r="Y2" t="n">
-        <v>259.52</v>
+        <v>234.77</v>
       </c>
       <c r="Z2" t="n">
-        <v>208.98</v>
+        <v>163.19</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -730,27 +730,27 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>273.53</v>
+        <v>252.19</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>18h-20h</t>
+          <t>20h-22h</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>299.15</v>
+        <v>261.42</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>20h-22h</t>
+          <t>0h-2h</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>284.13</v>
+        <v>253.34</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9h-16h</t>
+          <t>9h-17h</t>
         </is>
       </c>
     </row>
